--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:10</v>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -2681,7 +2681,7 @@
         <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:09</v>
@@ -2985,7 +2985,7 @@
         <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:11</v>
@@ -2605,19 +2605,19 @@
         <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B59" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:02</v>
@@ -2643,19 +2643,19 @@
         <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B60" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>4:20</v>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B80" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:14</v>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E193" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -705,7 +705,7 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>7:48</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -2529,7 +2529,7 @@
         <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:09</v>
@@ -3365,7 +3365,7 @@
         <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B79" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>10:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1465,7 +1465,7 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:17</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:21</v>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -1541,7 +1541,7 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>6:58</v>
@@ -1579,7 +1579,7 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:29</v>
@@ -1617,7 +1617,7 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:14</v>
@@ -1655,7 +1655,7 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:51</v>
@@ -1693,7 +1693,7 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:10</v>
@@ -1731,7 +1731,7 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:26</v>
@@ -1769,7 +1769,7 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>2:51</v>
@@ -1807,7 +1807,7 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:26</v>
@@ -1845,7 +1845,7 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:06</v>
@@ -1883,7 +1883,7 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:04</v>
@@ -1921,7 +1921,7 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:03</v>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:38</v>
@@ -1997,7 +1997,7 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:29</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:32</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -2073,7 +2073,7 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:32</v>
@@ -2111,7 +2111,7 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:51</v>
@@ -2149,7 +2149,7 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:38</v>
@@ -2187,7 +2187,7 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B48" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:26</v>
@@ -2225,7 +2225,7 @@
         <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:57</v>
@@ -2263,7 +2263,7 @@
         <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:08</v>
@@ -2301,7 +2301,7 @@
         <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:53</v>
@@ -2339,7 +2339,7 @@
         <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:10</v>
@@ -2377,7 +2377,7 @@
         <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:58</v>
@@ -2415,7 +2415,7 @@
         <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>2:44</v>
@@ -2453,7 +2453,7 @@
         <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:25</v>
@@ -2491,7 +2491,7 @@
         <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>4:08</v>
@@ -2909,7 +2909,7 @@
         <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:33</v>
@@ -3289,7 +3289,7 @@
         <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:27</v>
@@ -3327,7 +3327,7 @@
         <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:25</v>
@@ -3631,7 +3631,7 @@
         <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:26</v>
@@ -4163,7 +4163,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:06</v>
@@ -4201,7 +4201,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:21</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1389,7 +1389,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:10</v>
@@ -1427,7 +1427,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:06</v>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -4125,7 +4125,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:54</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1351,7 +1351,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:37</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
@@ -1533,7 +1533,7 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
@@ -2065,7 +2065,7 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="45">
@@ -4087,7 +4087,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>4:37</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -2833,7 +2833,7 @@
         <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:56</v>
@@ -2871,7 +2871,7 @@
         <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:25</v>
@@ -3251,7 +3251,7 @@
         <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>5:00</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -2795,7 +2795,7 @@
         <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:51</v>
@@ -3745,7 +3745,7 @@
         <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>4:20</v>
@@ -3859,7 +3859,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:29</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>5:31</v>
+        <v>3:01</v>
       </c>
       <c r="H2" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H3" t="str">
-        <v>Mýa</v>
+        <v>mgk</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:03</v>
+        <v>5:31</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>2:49</v>
       </c>
       <c r="H5" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Mýa</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H6" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -647,7 +647,7 @@
         <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v>ENHYPEN</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:59</v>
+        <v>2:41</v>
       </c>
       <c r="H8" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:48</v>
+        <v>2:59</v>
       </c>
       <c r="H9" t="str">
-        <v>The Doobie Brothers</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:10</v>
+        <v>3:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -796,7 +796,7 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:57</v>
+        <v>7:48</v>
       </c>
       <c r="H11" t="str">
         <v>The Doobie Brothers</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:25</v>
+        <v>3:10</v>
       </c>
       <c r="H12" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:19</v>
+        <v>5:57</v>
       </c>
       <c r="H13" t="str">
-        <v>Michael Bolton</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:38</v>
+        <v>2:25</v>
       </c>
       <c r="H14" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:05</v>
+        <v>3:19</v>
       </c>
       <c r="H15" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:46</v>
+        <v>3:38</v>
       </c>
       <c r="H16" t="str">
-        <v>Jacob Collier</v>
+        <v>mgk</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:25</v>
+        <v>4:05</v>
       </c>
       <c r="H17" t="str">
-        <v>Victor Ray</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:11</v>
+        <v>5:46</v>
       </c>
       <c r="H18" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H19" t="str">
-        <v>The Warning</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:54</v>
+        <v>5:11</v>
       </c>
       <c r="H20" t="str">
-        <v>The Offspring</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:01</v>
+        <v>2:55</v>
       </c>
       <c r="H21" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Warning</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:55</v>
+        <v>4:54</v>
       </c>
       <c r="H22" t="str">
-        <v>HAUSER</v>
+        <v>The Offspring</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:43</v>
+        <v>5:01</v>
       </c>
       <c r="H23" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:53</v>
+        <v>3:55</v>
       </c>
       <c r="H24" t="str">
-        <v>Ultra Records</v>
+        <v>HAUSER</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Jillian Jacquline - Another Lover (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:30</v>
+        <v>3:43</v>
       </c>
       <c r="H25" t="str">
-        <v>Anja Kotar</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:37</v>
+        <v>2:53</v>
       </c>
       <c r="H26" t="str">
-        <v>Michael Bolton</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:10</v>
+        <v>3:30</v>
       </c>
       <c r="H27" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H28" t="str">
-        <v>Alan Walker</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:17</v>
+        <v>4:10</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H30" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>6:58</v>
+        <v>3:17</v>
       </c>
       <c r="H31" t="str">
-        <v>Eric Church</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H32" t="str">
-        <v>Meghan Trainor</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:14</v>
+        <v>6:58</v>
       </c>
       <c r="H33" t="str">
-        <v>Ally Salort</v>
+        <v>Eric Church</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:51</v>
+        <v>3:29</v>
       </c>
       <c r="H34" t="str">
-        <v>Will Swinton</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>elijah woods</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H36" t="str">
-        <v>Jackson Dean</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:51</v>
+        <v>3:10</v>
       </c>
       <c r="H37" t="str">
-        <v>Matteo Bocelli</v>
+        <v>elijah woods</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1825,7 +1825,7 @@
         <v>3:26</v>
       </c>
       <c r="H38" t="str">
-        <v>Neil Sedaka</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H39" t="str">
-        <v>Sofia Camara</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:04</v>
+        <v>3:26</v>
       </c>
       <c r="H40" t="str">
-        <v>Russell Dickerson</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Celine Dion</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:38</v>
+        <v>3:04</v>
       </c>
       <c r="H42" t="str">
-        <v>Bebe Rexha</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:29</v>
+        <v>3:03</v>
       </c>
       <c r="H43" t="str">
-        <v>Caroline Jones</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:32</v>
+        <v>2:38</v>
       </c>
       <c r="H44" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>3:29</v>
       </c>
       <c r="H45" t="str">
-        <v>Ingrid Andress</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:51</v>
+        <v>2:32</v>
       </c>
       <c r="H46" t="str">
-        <v>MusicByKnox</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:38</v>
+        <v>3:32</v>
       </c>
       <c r="H47" t="str">
-        <v>Ella Langley</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H48" t="str">
-        <v>Nickless</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2240,10 +2240,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:57</v>
+        <v>3:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Caroline Jones</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2278,10 +2278,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:08</v>
+        <v>3:26</v>
       </c>
       <c r="H50" t="str">
-        <v>elijah woods</v>
+        <v>Nickless</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2316,10 +2316,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:53</v>
+        <v>3:57</v>
       </c>
       <c r="H51" t="str">
-        <v>August Ponthier</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2354,10 +2354,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:08</v>
       </c>
       <c r="H52" t="str">
-        <v>Charli xcx</v>
+        <v>elijah woods</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2392,10 +2392,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:58</v>
+        <v>3:53</v>
       </c>
       <c r="H53" t="str">
-        <v>Caroline Jones</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2430,10 +2430,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H54" t="str">
-        <v>Leah Kate</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2468,10 +2468,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:25</v>
+        <v>2:58</v>
       </c>
       <c r="H55" t="str">
-        <v>Troye Sivan</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2506,10 +2506,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:08</v>
+        <v>2:44</v>
       </c>
       <c r="H56" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2544,10 +2544,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:09</v>
+        <v>3:25</v>
       </c>
       <c r="H57" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2582,10 +2582,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:11</v>
+        <v>4:08</v>
       </c>
       <c r="H58" t="str">
-        <v>The Happy Fits</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2620,10 +2620,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:02</v>
+        <v>3:09</v>
       </c>
       <c r="H59" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2658,10 +2658,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:20</v>
+        <v>3:11</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B61" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2696,10 +2696,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:09</v>
+        <v>3:02</v>
       </c>
       <c r="H61" t="str">
-        <v>Quinn XCII</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B62" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2734,10 +2734,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:34</v>
+        <v>4:20</v>
       </c>
       <c r="H62" t="str">
-        <v>We Three</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B63" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2772,10 +2772,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:29</v>
+        <v>4:09</v>
       </c>
       <c r="H63" t="str">
-        <v>A Thousand Horses</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:51</v>
+        <v>4:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>We Three</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:56</v>
+        <v>3:29</v>
       </c>
       <c r="H65" t="str">
-        <v>Constant Smiles</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B66" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2886,10 +2886,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>2:51</v>
       </c>
       <c r="H66" t="str">
-        <v>P!NK</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2924,10 +2924,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>2:56</v>
       </c>
       <c r="H67" t="str">
-        <v>Bazzi</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B68" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2962,10 +2962,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:18</v>
+        <v>3:25</v>
       </c>
       <c r="H68" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>P!NK</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -3000,10 +3000,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:08</v>
+        <v>2:33</v>
       </c>
       <c r="H69" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B70" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3038,10 +3038,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:56</v>
+        <v>4:18</v>
       </c>
       <c r="H70" t="str">
-        <v>bleachers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B71" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3076,10 +3076,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:27</v>
+        <v>2:08</v>
       </c>
       <c r="H71" t="str">
-        <v>The Academic</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3114,10 +3114,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:39</v>
+        <v>3:56</v>
       </c>
       <c r="H72" t="str">
-        <v>Louis Tomlinson</v>
+        <v>bleachers</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3152,10 +3152,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:54</v>
+        <v>3:27</v>
       </c>
       <c r="H73" t="str">
-        <v>Michael Bolton</v>
+        <v>The Academic</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3190,10 +3190,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:47</v>
+        <v>2:39</v>
       </c>
       <c r="H74" t="str">
-        <v>Caroline Jones</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3228,10 +3228,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:07</v>
+        <v>3:54</v>
       </c>
       <c r="H75" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:00</v>
+        <v>3:47</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:27</v>
+        <v>4:07</v>
       </c>
       <c r="H77" t="str">
-        <v>Little Big Town</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3342,10 +3342,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:25</v>
+        <v>5:00</v>
       </c>
       <c r="H78" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3380,10 +3380,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>10:57</v>
+        <v>3:27</v>
       </c>
       <c r="H79" t="str">
-        <v>JavaJazzFest</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3418,10 +3418,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:14</v>
+        <v>3:25</v>
       </c>
       <c r="H80" t="str">
-        <v>Robert Grace</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3456,10 +3456,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:26</v>
+        <v>10:57</v>
       </c>
       <c r="H81" t="str">
-        <v>mgk</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3494,10 +3494,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:59</v>
+        <v>4:14</v>
       </c>
       <c r="H82" t="str">
-        <v>Victor Ray</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>3:26</v>
       </c>
       <c r="H83" t="str">
-        <v>Perrie</v>
+        <v>mgk</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:39</v>
+        <v>5:59</v>
       </c>
       <c r="H84" t="str">
-        <v>Michael Bolton</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:58</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Perrie</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:26</v>
+        <v>3:39</v>
       </c>
       <c r="H86" t="str">
-        <v>Mimi Webb</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>3:58</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>6:00</v>
+        <v>2:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Taylor Swift</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:20</v>
+        <v>3:04</v>
       </c>
       <c r="H89" t="str">
-        <v>Michael Bolton</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3798,10 +3798,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:27</v>
+        <v>6:00</v>
       </c>
       <c r="H90" t="str">
-        <v>Mariah Carey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>4:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:29</v>
+        <v>4:27</v>
       </c>
       <c r="H92" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B93" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-16</v>
@@ -3912,10 +3912,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:59</v>
+        <v>3:26</v>
       </c>
       <c r="H93" t="str">
-        <v>mgk</v>
+        <v>Netflix</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-16</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H94" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-16</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:13</v>
+        <v>2:59</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-16</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:41</v>
+        <v>2:51</v>
       </c>
       <c r="H96" t="str">
-        <v>NICK JONAS</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-16</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>7:03</v>
+        <v>4:13</v>
       </c>
       <c r="H97" t="str">
-        <v>Take That</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-16</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:37</v>
+        <v>4:41</v>
       </c>
       <c r="H98" t="str">
-        <v>Cliff Richard</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-16</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:54</v>
+        <v>7:03</v>
       </c>
       <c r="H99" t="str">
-        <v>Bryan Adams</v>
+        <v>Take That</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-16</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:06</v>
+        <v>4:37</v>
       </c>
       <c r="H100" t="str">
-        <v>Anna Graves</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-16</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:21</v>
+        <v>3:54</v>
       </c>
       <c r="H101" t="str">
-        <v>George Birge</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -3669,7 +3669,7 @@
         <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>3:58</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:28</v>
@@ -705,7 +705,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:59</v>
@@ -1275,7 +1275,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:55</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3555,7 +3555,7 @@
         <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>5:59</v>
@@ -3631,7 +3631,7 @@
         <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:39</v>
@@ -4049,7 +4049,7 @@
         <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:13</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:28</v>
@@ -1237,7 +1237,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>5:01</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
@@ -1343,7 +1343,7 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jillian Jacquline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="26">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2833,7 +2833,7 @@
         <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:29</v>
@@ -4011,7 +4011,7 @@
         <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>2:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:28</v>
@@ -515,7 +515,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:31</v>
@@ -667,7 +667,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:41</v>
@@ -1123,7 +1123,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:11</v>
@@ -1161,7 +1161,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:55</v>
@@ -1199,7 +1199,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>4:54</v>
@@ -1351,7 +1351,7 @@
         <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:53</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3251,7 +3251,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:47</v>
@@ -3289,7 +3289,7 @@
         <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:07</v>
@@ -3593,7 +3593,7 @@
         <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:46</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Always Everywhere</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Wuthering Heights</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:03</v>
+        <v>3:14</v>
       </c>
       <c r="H102" t="str">
-        <v>Charli xcx</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L102" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Be Her</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G103" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L103" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-16</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H104" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-16</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G105" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H105" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L105" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H106" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L106" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Trying Times</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:40</v>
+        <v>3:00</v>
       </c>
       <c r="H107" t="str">
-        <v>James Blake</v>
+        <v>CORTIS</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L107" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G108" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H108" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L108" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H109" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L109" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H110" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L110" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G111" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L111" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H112" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L112" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H113" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L113" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H114" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L114" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-16</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H115" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L115" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H116" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L116" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G117" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L117" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H118" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L118" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L119" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L120" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G121" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H121" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L121" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H122" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L122" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G123" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H123" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L123" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G124" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H124" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L124" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L125" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G126" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H126" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L126" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H127" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L127" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L128" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L129" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G130" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H130" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L130" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H131" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L131" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L132" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G133" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H133" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L133" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H134" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L134" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H135" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L135" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L136" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H137" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L137" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G138" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H138" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L138" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H139" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L139" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H140" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L140" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H141" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L141" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L142" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G143" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H143" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L143" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H144" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L144" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H145" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L145" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G146" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H146" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L146" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H147" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L147" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H148" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L148" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G149" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H149" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L149" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G150" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H150" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L150" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H151" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L151" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H152" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L152" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G153" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H153" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L153" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L154" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L155" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L156" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H157" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L157" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H158" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L158" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H159" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L159" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H160" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L160" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L161" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L162" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G163" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L163" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G164" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H164" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L164" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G165" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H165" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L165" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L166" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L167" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L168" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H169" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L169" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H170" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L170" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H171" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L171" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H172" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L172" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G173" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L173" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H174" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L174" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G175" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L175" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H176" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L176" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H177" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L177" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L178" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G179" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H179" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L179" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G180" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H180" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L180" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H181" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L181" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G182" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L182" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G183" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H183" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L183" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H184" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L184" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H185" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L185" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H186" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L186" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H187" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L187" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G188" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H188" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L188" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H189" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L189" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H190" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L190" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G191" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H191" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L191" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-16</v>
@@ -7671,68 +7671,106 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G192" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H192" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L192" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G193" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D194" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G194" t="str">
         <v>3:17</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H194" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K194" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L194" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -477,7 +477,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:03</v>
@@ -629,7 +629,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:59</v>
@@ -895,7 +895,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:25</v>
@@ -933,7 +933,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:19</v>
@@ -971,7 +971,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:38</v>
@@ -1009,7 +1009,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:05</v>
@@ -1047,7 +1047,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:46</v>
@@ -1085,7 +1085,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:25</v>
@@ -1389,7 +1389,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:30</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2795,7 +2795,7 @@
         <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:34</v>
@@ -3137,7 +3137,7 @@
         <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:27</v>
@@ -3175,7 +3175,7 @@
         <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:39</v>
@@ -3213,7 +3213,7 @@
         <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:54</v>
@@ -3517,7 +3517,7 @@
         <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:26</v>
@@ -3745,7 +3745,7 @@
         <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:04</v>
@@ -3973,7 +3973,7 @@
         <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3099,7 +3099,7 @@
         <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -553,7 +553,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:49</v>
@@ -857,7 +857,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>5:57</v>
@@ -1313,7 +1313,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:43</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3859,7 +3859,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B92" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3023,7 +3023,7 @@
         <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>4:18</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -819,7 +819,7 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:10</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2757,7 +2757,7 @@
         <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B63" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:09</v>
@@ -3061,7 +3061,7 @@
         <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,19 +439,19 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:11</v>
@@ -2681,19 +2681,19 @@
         <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B61" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:02</v>
@@ -2719,19 +2719,19 @@
         <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B62" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:20</v>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B82" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>4:14</v>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E194" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -781,7 +781,7 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>7:48</v>
@@ -2605,7 +2605,7 @@
         <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B59" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:09</v>
@@ -3441,7 +3441,7 @@
         <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B81" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>10:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1541,7 +1541,7 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:17</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:21</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -1617,7 +1617,7 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>6:58</v>
@@ -1655,7 +1655,7 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:29</v>
@@ -1693,7 +1693,7 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:14</v>
@@ -1731,7 +1731,7 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:51</v>
@@ -1769,7 +1769,7 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:10</v>
@@ -1807,7 +1807,7 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:26</v>
@@ -1845,7 +1845,7 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:51</v>
@@ -1883,7 +1883,7 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:26</v>
@@ -1921,7 +1921,7 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:06</v>
@@ -1959,7 +1959,7 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:04</v>
@@ -1997,7 +1997,7 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:03</v>
@@ -2035,7 +2035,7 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:38</v>
@@ -2073,7 +2073,7 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:29</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:32</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2149,7 +2149,7 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:32</v>
@@ -2187,7 +2187,7 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:51</v>
@@ -2225,7 +2225,7 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:38</v>
@@ -2263,7 +2263,7 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:26</v>
@@ -2301,7 +2301,7 @@
         <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:57</v>
@@ -2339,7 +2339,7 @@
         <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:08</v>
@@ -2377,7 +2377,7 @@
         <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:53</v>
@@ -2415,7 +2415,7 @@
         <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:10</v>
@@ -2453,7 +2453,7 @@
         <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>2:58</v>
@@ -2491,7 +2491,7 @@
         <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:44</v>
@@ -2529,7 +2529,7 @@
         <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:25</v>
@@ -2567,7 +2567,7 @@
         <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>4:08</v>
@@ -2985,7 +2985,7 @@
         <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:33</v>
@@ -3365,7 +3365,7 @@
         <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B79" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:27</v>
@@ -3403,7 +3403,7 @@
         <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:25</v>
@@ -3707,7 +3707,7 @@
         <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>2:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1465,7 +1465,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>4:10</v>
@@ -1503,7 +1503,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:06</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -4201,7 +4201,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:54</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1427,7 +1427,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:37</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -4163,7 +4163,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>4:37</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2909,7 +2909,7 @@
         <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:56</v>
@@ -2947,7 +2947,7 @@
         <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>3:25</v>
@@ -3327,7 +3327,7 @@
         <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>5:00</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:01</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2871,7 +2871,7 @@
         <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:51</v>
@@ -3821,7 +3821,7 @@
         <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>4:20</v>
@@ -3935,7 +3935,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:29</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:59</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3631,7 +3631,7 @@
         <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:39</v>
@@ -3669,7 +3669,7 @@
         <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>3:58</v>
@@ -3783,7 +3783,7 @@
         <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>6:00</v>
@@ -3897,7 +3897,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:26</v>
@@ -4087,7 +4087,7 @@
         <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>4:41</v>
@@ -4125,7 +4125,7 @@
         <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>7:03</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -705,7 +705,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:59</v>
@@ -1275,7 +1275,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:55</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -3555,7 +3555,7 @@
         <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>5:59</v>
@@ -4049,7 +4049,7 @@
         <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:13</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1237,7 +1237,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>5:01</v>
@@ -2833,7 +2833,7 @@
         <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:29</v>
@@ -3289,7 +3289,7 @@
         <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:07</v>
@@ -4011,7 +4011,7 @@
         <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>2:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -515,7 +515,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:31</v>
@@ -667,7 +667,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:41</v>
@@ -1123,7 +1123,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:11</v>
@@ -1161,7 +1161,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:55</v>
@@ -1199,7 +1199,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>4:54</v>
@@ -1351,7 +1351,7 @@
         <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:53</v>
@@ -3251,7 +3251,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:47</v>
@@ -3593,7 +3593,7 @@
         <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:46</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-17</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G102" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H102" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L102" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="103">
@@ -4464,13 +4464,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-17</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Trying Times</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:40</v>
+        <v>3:14</v>
       </c>
       <c r="H108" t="str">
-        <v>James Blake</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L108" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-17</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G109" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H109" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L109" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-17</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H110" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L110" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-17</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H111" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L111" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-17</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G112" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H112" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L112" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-17</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H113" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L113" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-17</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H114" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L114" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-17</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H115" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L115" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-17</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H116" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L116" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-17</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H117" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L117" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-17</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G118" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H118" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L118" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-17</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G119" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H119" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L119" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-17</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L120" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-17</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H121" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L121" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-17</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G122" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H122" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L122" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-17</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H123" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L123" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-17</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G124" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H124" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L124" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-17</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G125" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H125" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L125" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-17</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H126" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L126" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-17</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G127" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H127" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L127" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-17</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H128" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L128" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-17</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H129" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L129" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-17</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H130" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L130" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-17</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G131" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H131" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L131" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-17</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H132" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L132" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-17</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H133" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L133" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-17</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G134" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H134" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L134" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-17</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H135" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L135" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-17</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H136" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L136" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-17</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L137" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-17</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H138" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L138" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-17</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G139" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L139" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-17</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H140" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L140" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-17</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H141" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L141" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-17</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H142" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L142" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-17</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H143" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L143" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-17</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G144" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H144" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L144" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-17</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H145" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L145" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-17</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H146" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L146" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-17</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G147" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H147" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L147" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-17</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H148" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L148" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-17</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H149" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L149" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-17</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G150" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H150" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L150" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-17</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G151" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H151" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L151" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-17</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H152" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L152" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-17</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G153" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H153" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L153" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-17</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G154" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H154" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L154" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-17</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G155" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L155" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-17</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H156" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L156" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-17</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H157" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L157" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-17</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H158" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L158" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-17</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H159" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L159" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-17</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H160" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L160" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-17</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H161" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L161" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-17</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H162" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L162" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-17</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L163" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-17</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G164" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H164" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L164" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-17</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G165" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H165" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L165" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-17</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G166" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H166" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L166" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-17</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L167" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-17</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H168" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L168" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-17</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H169" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L169" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-17</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H170" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L170" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-17</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H171" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L171" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-17</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H172" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L172" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-17</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H173" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L173" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-17</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G174" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H174" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L174" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-17</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H175" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L175" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-17</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G176" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H176" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L176" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-17</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H177" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L177" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-17</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H178" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L178" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-17</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L179" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-17</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G180" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H180" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L180" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-17</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G181" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H181" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L181" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-17</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H182" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L182" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-17</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G183" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H183" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L183" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-17</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G184" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H184" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L184" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-17</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H185" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L185" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-17</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H186" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L186" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-17</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H187" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L187" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-17</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H188" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L188" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-17</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G189" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H189" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L189" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-17</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G190" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H190" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L190" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-17</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H191" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L191" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-17</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G192" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H192" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L192" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-17</v>
@@ -7709,68 +7709,106 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G193" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L193" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G194" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K194" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D194" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
+      <c r="D195" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G194" t="str">
+      <c r="G195" t="str">
         <v>3:17</v>
       </c>
-      <c r="H194" t="str">
+      <c r="H195" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K194" t="str">
+      <c r="K195" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L194" t="str">
+      <c r="L195" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:28</v>
@@ -591,7 +591,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:03</v>
@@ -629,7 +629,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:59</v>
@@ -895,7 +895,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:25</v>
@@ -933,7 +933,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:19</v>
@@ -971,7 +971,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:38</v>
@@ -1009,7 +1009,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:05</v>
@@ -1047,7 +1047,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:46</v>
@@ -1085,7 +1085,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:25</v>
@@ -1389,7 +1389,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:30</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="47">
@@ -2795,7 +2795,7 @@
         <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:34</v>
@@ -3137,7 +3137,7 @@
         <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:27</v>
@@ -3175,7 +3175,7 @@
         <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:39</v>
@@ -3213,7 +3213,7 @@
         <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:54</v>
@@ -3517,7 +3517,7 @@
         <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:26</v>
@@ -3745,7 +3745,7 @@
         <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B89" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:04</v>
@@ -3973,7 +3973,7 @@
         <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B2" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -454,10 +454,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:01</v>
+        <v>4:11</v>
       </c>
       <c r="H2" t="str">
-        <v>The Vaccines</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H3" t="str">
-        <v>mgk</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H4" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H5" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H6" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B7" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-17</v>
@@ -644,10 +644,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H7" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B8" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-17</v>
@@ -682,10 +682,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H8" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-17</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H9" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-17</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-17</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H11" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-17</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H12" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-17</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H13" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-17</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H14" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B15" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-17</v>
@@ -948,10 +948,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H15" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-17</v>
@@ -986,10 +986,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H16" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-17</v>
@@ -1024,10 +1024,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H17" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-17</v>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-17</v>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H19" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-17</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H20" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-17</v>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-17</v>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H22" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-17</v>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H23" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-17</v>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H24" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-17</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H25" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>11 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-17</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>11 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H26" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-17</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H27" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-17</v>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H28" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-17</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H29" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-17</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H30" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-17</v>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H31" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-17</v>
@@ -1594,10 +1594,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H32" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-17</v>
@@ -1632,10 +1632,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H33" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-17</v>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H34" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-17</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H35" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-17</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H36" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-17</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H37" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-17</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-17</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H39" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-17</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H40" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-17</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-17</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H42" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-17</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H43" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-17</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H44" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-17</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H45" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-17</v>
@@ -2126,10 +2126,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-17</v>
@@ -2164,10 +2164,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H47" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B48" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-17</v>
@@ -2202,10 +2202,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H48" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-17</v>
@@ -2240,10 +2240,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H49" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B50" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-17</v>
@@ -2278,10 +2278,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H50" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-17</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H51" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-17</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H52" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-17</v>
@@ -2392,10 +2392,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H53" t="str">
-        <v>August Ponthier</v>
+        <v>elijah woods</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-17</v>
@@ -2430,10 +2430,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:10</v>
+        <v>3:53</v>
       </c>
       <c r="H54" t="str">
-        <v>Charli xcx</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-17</v>
@@ -2468,10 +2468,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:58</v>
+        <v>3:10</v>
       </c>
       <c r="H55" t="str">
-        <v>Caroline Jones</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-17</v>
@@ -2506,10 +2506,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:44</v>
+        <v>2:58</v>
       </c>
       <c r="H56" t="str">
-        <v>Leah Kate</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-17</v>
@@ -2544,10 +2544,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:25</v>
+        <v>2:44</v>
       </c>
       <c r="H57" t="str">
-        <v>Troye Sivan</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B58" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-17</v>
@@ -2582,10 +2582,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:08</v>
+        <v>3:25</v>
       </c>
       <c r="H58" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B59" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-17</v>
@@ -2620,10 +2620,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:09</v>
+        <v>4:08</v>
       </c>
       <c r="H59" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B60" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-17</v>
@@ -2658,10 +2658,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H60" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-17</v>
@@ -2696,10 +2696,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:02</v>
+        <v>3:11</v>
       </c>
       <c r="H61" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B62" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-17</v>
@@ -2734,10 +2734,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:20</v>
+        <v>3:02</v>
       </c>
       <c r="H62" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B63" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-17</v>
@@ -2772,10 +2772,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:09</v>
+        <v>4:20</v>
       </c>
       <c r="H63" t="str">
-        <v>Quinn XCII</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B64" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-17</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:34</v>
+        <v>4:09</v>
       </c>
       <c r="H64" t="str">
-        <v>We Three</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B65" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-17</v>
@@ -2848,10 +2848,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:29</v>
+        <v>4:34</v>
       </c>
       <c r="H65" t="str">
-        <v>A Thousand Horses</v>
+        <v>We Three</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B66" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-17</v>
@@ -2886,10 +2886,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H66" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-17</v>
@@ -2924,10 +2924,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H67" t="str">
-        <v>Constant Smiles</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-17</v>
@@ -2962,10 +2962,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H68" t="str">
-        <v>P!NK</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B69" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-17</v>
@@ -3000,10 +3000,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:33</v>
+        <v>3:25</v>
       </c>
       <c r="H69" t="str">
-        <v>Bazzi</v>
+        <v>P!NK</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-17</v>
@@ -3038,10 +3038,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:18</v>
+        <v>2:33</v>
       </c>
       <c r="H70" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B71" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-17</v>
@@ -3076,7 +3076,7 @@
         <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:08</v>
+        <v>4:18</v>
       </c>
       <c r="H71" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B72" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-17</v>
@@ -3114,10 +3114,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:56</v>
+        <v>2:08</v>
       </c>
       <c r="H72" t="str">
-        <v>bleachers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-17</v>
@@ -3152,10 +3152,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:27</v>
+        <v>3:56</v>
       </c>
       <c r="H73" t="str">
-        <v>The Academic</v>
+        <v>bleachers</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-17</v>
@@ -3190,10 +3190,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:39</v>
+        <v>3:27</v>
       </c>
       <c r="H74" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Academic</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-17</v>
@@ -3228,10 +3228,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:54</v>
+        <v>2:39</v>
       </c>
       <c r="H75" t="str">
-        <v>Michael Bolton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-17</v>
@@ -3266,10 +3266,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:47</v>
+        <v>3:54</v>
       </c>
       <c r="H76" t="str">
-        <v>Caroline Jones</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B77" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-17</v>
@@ -3304,10 +3304,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:07</v>
+        <v>3:47</v>
       </c>
       <c r="H77" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B78" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-17</v>
@@ -3342,10 +3342,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>5:00</v>
+        <v>4:07</v>
       </c>
       <c r="H78" t="str">
-        <v>Michael Bolton</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-17</v>
@@ -3380,10 +3380,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:27</v>
+        <v>5:00</v>
       </c>
       <c r="H79" t="str">
-        <v>Little Big Town</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B80" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-17</v>
@@ -3418,10 +3418,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H80" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-17</v>
@@ -3456,10 +3456,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>10:57</v>
+        <v>3:25</v>
       </c>
       <c r="H81" t="str">
-        <v>JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B82" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-17</v>
@@ -3494,10 +3494,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:14</v>
+        <v>10:57</v>
       </c>
       <c r="H82" t="str">
-        <v>Robert Grace</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B83" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-17</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:26</v>
+        <v>4:14</v>
       </c>
       <c r="H83" t="str">
-        <v>mgk</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-17</v>
@@ -3570,10 +3570,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>5:59</v>
+        <v>3:26</v>
       </c>
       <c r="H84" t="str">
-        <v>Victor Ray</v>
+        <v>mgk</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B85" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-17</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>5:59</v>
       </c>
       <c r="H85" t="str">
-        <v>Perrie</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B86" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-17</v>
@@ -3646,10 +3646,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:39</v>
+        <v>2:46</v>
       </c>
       <c r="H86" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-17</v>
@@ -3684,10 +3684,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:58</v>
+        <v>3:39</v>
       </c>
       <c r="H87" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-17</v>
@@ -3722,10 +3722,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:26</v>
+        <v>3:58</v>
       </c>
       <c r="H88" t="str">
-        <v>Mimi Webb</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-17</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:04</v>
+        <v>2:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Olivia Dean</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B90" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-17</v>
@@ -3798,10 +3798,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H90" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-17</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H91" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B92" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-17</v>
@@ -3874,10 +3874,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H92" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-17</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-17</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H94" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-17</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H95" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-17</v>
@@ -4026,10 +4026,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H96" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B97" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-17</v>
@@ -4064,10 +4064,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H97" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-17</v>
@@ -4102,10 +4102,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H98" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B99" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-17</v>
@@ -4140,10 +4140,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H99" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B100" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-17</v>
@@ -4178,10 +4178,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H100" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B101" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-17</v>
@@ -4216,10 +4216,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H101" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:49</v>
@@ -895,7 +895,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>5:57</v>
@@ -1351,7 +1351,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:43</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
@@ -1647,7 +1647,7 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="34">
@@ -3897,7 +3897,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H2" t="str">
-        <v>Holly Humberstone</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES FEBRUARY 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=llKawYldOdg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:01</v>
+        <v>1:00:47</v>
       </c>
       <c r="H3" t="str">
-        <v>The Vaccines</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES FEBRUARY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:28</v>
+        <v>4:26</v>
       </c>
       <c r="H4" t="str">
-        <v>mgk</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:31</v>
+        <v>4:35</v>
       </c>
       <c r="H5" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:49</v>
+        <v>4:11</v>
       </c>
       <c r="H6" t="str">
-        <v>Mýa</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-17</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:03</v>
+        <v>3:01</v>
       </c>
       <c r="H7" t="str">
-        <v>Michael Bolton</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-17</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:59</v>
+        <v>3:28</v>
       </c>
       <c r="H8" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>mgk</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-17</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:41</v>
+        <v>5:31</v>
       </c>
       <c r="H9" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-17</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:59</v>
+        <v>2:49</v>
       </c>
       <c r="H10" t="str">
-        <v>ENHYPEN</v>
+        <v>Mýa</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-17</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:59</v>
+        <v>3:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-17</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>7:48</v>
+        <v>2:59</v>
       </c>
       <c r="H12" t="str">
-        <v>The Doobie Brothers</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-17</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:10</v>
+        <v>2:41</v>
       </c>
       <c r="H13" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-17</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:57</v>
+        <v>2:59</v>
       </c>
       <c r="H14" t="str">
-        <v>The Doobie Brothers</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-17</v>
@@ -945,10 +945,10 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:25</v>
+        <v>3:59</v>
       </c>
       <c r="H15" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-17</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:19</v>
+        <v>7:48</v>
       </c>
       <c r="H16" t="str">
-        <v>Michael Bolton</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-17</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H17" t="str">
-        <v>mgk</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-17</v>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>5:57</v>
       </c>
       <c r="H18" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-17</v>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:46</v>
+        <v>2:25</v>
       </c>
       <c r="H19" t="str">
-        <v>Jacob Collier</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-17</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:25</v>
+        <v>3:19</v>
       </c>
       <c r="H20" t="str">
-        <v>Victor Ray</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-17</v>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:11</v>
+        <v>3:38</v>
       </c>
       <c r="H21" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>mgk</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-17</v>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:55</v>
+        <v>4:05</v>
       </c>
       <c r="H22" t="str">
-        <v>The Warning</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-17</v>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:54</v>
+        <v>5:46</v>
       </c>
       <c r="H23" t="str">
-        <v>The Offspring</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-17</v>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>5:01</v>
+        <v>3:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-17</v>
@@ -1328,10 +1328,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:55</v>
+        <v>5:11</v>
       </c>
       <c r="H25" t="str">
-        <v>HAUSER</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-17</v>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:43</v>
+        <v>2:55</v>
       </c>
       <c r="H26" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>The Warning</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-17</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:53</v>
+        <v>4:54</v>
       </c>
       <c r="H27" t="str">
-        <v>Ultra Records</v>
+        <v>The Offspring</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-17</v>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:30</v>
+        <v>5:01</v>
       </c>
       <c r="H28" t="str">
-        <v>Anja Kotar</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-17</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:37</v>
+        <v>3:55</v>
       </c>
       <c r="H29" t="str">
-        <v>Michael Bolton</v>
+        <v>HAUSER</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-17</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:10</v>
+        <v>3:43</v>
       </c>
       <c r="H30" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-17</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:06</v>
+        <v>2:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Alan Walker</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-17</v>
@@ -1594,10 +1594,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:17</v>
+        <v>3:30</v>
       </c>
       <c r="H32" t="str">
-        <v>Bruno Mars</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-17</v>
@@ -1632,10 +1632,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:21</v>
+        <v>3:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-17</v>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>6:58</v>
+        <v>4:10</v>
       </c>
       <c r="H34" t="str">
-        <v>Eric Church</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-17</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:29</v>
+        <v>3:06</v>
       </c>
       <c r="H35" t="str">
-        <v>Meghan Trainor</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-17</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H36" t="str">
-        <v>Ally Salort</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-17</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:51</v>
+        <v>3:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Will Swinton</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-17</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:10</v>
+        <v>6:58</v>
       </c>
       <c r="H38" t="str">
-        <v>elijah woods</v>
+        <v>Eric Church</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-17</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H39" t="str">
-        <v>Jackson Dean</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-17</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:51</v>
+        <v>3:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-17</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H41" t="str">
-        <v>Neil Sedaka</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-17</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:06</v>
+        <v>3:10</v>
       </c>
       <c r="H42" t="str">
-        <v>Sofia Camara</v>
+        <v>elijah woods</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-17</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:04</v>
+        <v>3:26</v>
       </c>
       <c r="H43" t="str">
-        <v>Russell Dickerson</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-17</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:03</v>
+        <v>2:51</v>
       </c>
       <c r="H44" t="str">
-        <v>Celine Dion</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-17</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:38</v>
+        <v>3:26</v>
       </c>
       <c r="H45" t="str">
-        <v>Bebe Rexha</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-17</v>
@@ -2126,10 +2126,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:29</v>
+        <v>3:06</v>
       </c>
       <c r="H46" t="str">
-        <v>Caroline Jones</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-17</v>
@@ -2164,10 +2164,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:32</v>
+        <v>3:04</v>
       </c>
       <c r="H47" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B48" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-17</v>
@@ -2202,10 +2202,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:32</v>
+        <v>3:03</v>
       </c>
       <c r="H48" t="str">
-        <v>Ingrid Andress</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-17</v>
@@ -2240,10 +2240,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H49" t="str">
-        <v>MusicByKnox</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-17</v>
@@ -2278,10 +2278,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:38</v>
+        <v>3:29</v>
       </c>
       <c r="H50" t="str">
-        <v>Ella Langley</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-17</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:26</v>
+        <v>2:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Nickless</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-17</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:57</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>Caroline Jones</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-17</v>
@@ -2392,10 +2392,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:08</v>
+        <v>2:51</v>
       </c>
       <c r="H53" t="str">
-        <v>elijah woods</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-17</v>
@@ -2430,10 +2430,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:53</v>
+        <v>3:38</v>
       </c>
       <c r="H54" t="str">
-        <v>August Ponthier</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B55" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-17</v>
@@ -2468,10 +2468,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H55" t="str">
-        <v>Charli xcx</v>
+        <v>Nickless</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-17</v>
@@ -2506,7 +2506,7 @@
         <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:58</v>
+        <v>3:57</v>
       </c>
       <c r="H56" t="str">
         <v>Caroline Jones</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-17</v>
@@ -2544,10 +2544,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:44</v>
+        <v>3:08</v>
       </c>
       <c r="H57" t="str">
-        <v>Leah Kate</v>
+        <v>elijah woods</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-17</v>
@@ -2582,10 +2582,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:25</v>
+        <v>3:53</v>
       </c>
       <c r="H58" t="str">
-        <v>Troye Sivan</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-17</v>
@@ -2620,10 +2620,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:08</v>
+        <v>3:10</v>
       </c>
       <c r="H59" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-17</v>
@@ -2658,10 +2658,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:09</v>
+        <v>2:58</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-17</v>
@@ -2696,10 +2696,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:11</v>
+        <v>2:44</v>
       </c>
       <c r="H61" t="str">
-        <v>The Happy Fits</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-17</v>
@@ -2734,10 +2734,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:02</v>
+        <v>3:25</v>
       </c>
       <c r="H62" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-17</v>
@@ -2772,10 +2772,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:20</v>
+        <v>4:08</v>
       </c>
       <c r="H63" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B64" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-17</v>
@@ -2810,10 +2810,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:09</v>
+        <v>3:09</v>
       </c>
       <c r="H64" t="str">
-        <v>Quinn XCII</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-17</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:34</v>
+        <v>3:11</v>
       </c>
       <c r="H65" t="str">
-        <v>We Three</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B66" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-17</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:29</v>
+        <v>3:02</v>
       </c>
       <c r="H66" t="str">
-        <v>A Thousand Horses</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B67" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-17</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:51</v>
+        <v>4:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-17</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:56</v>
+        <v>4:09</v>
       </c>
       <c r="H68" t="str">
-        <v>Constant Smiles</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B69" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-17</v>
@@ -3000,10 +3000,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:25</v>
+        <v>4:34</v>
       </c>
       <c r="H69" t="str">
-        <v>P!NK</v>
+        <v>We Three</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B70" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-17</v>
@@ -3038,10 +3038,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:33</v>
+        <v>3:29</v>
       </c>
       <c r="H70" t="str">
-        <v>Bazzi</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-17</v>
@@ -3076,10 +3076,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:18</v>
+        <v>2:51</v>
       </c>
       <c r="H71" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-17</v>
@@ -3114,10 +3114,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:08</v>
+        <v>2:56</v>
       </c>
       <c r="H72" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B73" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-17</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:56</v>
+        <v>3:25</v>
       </c>
       <c r="H73" t="str">
-        <v>bleachers</v>
+        <v>P!NK</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-17</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H74" t="str">
-        <v>The Academic</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-17</v>
@@ -3228,10 +3228,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H75" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-17</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:54</v>
+        <v>2:08</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-17</v>
@@ -3304,10 +3304,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:47</v>
+        <v>3:56</v>
       </c>
       <c r="H77" t="str">
-        <v>Caroline Jones</v>
+        <v>bleachers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-17</v>
@@ -3342,10 +3342,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:07</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>The Academic</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-17</v>
@@ -3380,10 +3380,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>5:00</v>
+        <v>2:39</v>
       </c>
       <c r="H79" t="str">
-        <v>Michael Bolton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-17</v>
@@ -3418,10 +3418,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:27</v>
+        <v>3:54</v>
       </c>
       <c r="H80" t="str">
-        <v>Little Big Town</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B81" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-17</v>
@@ -3456,10 +3456,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:25</v>
+        <v>3:47</v>
       </c>
       <c r="H81" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B82" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-17</v>
@@ -3494,10 +3494,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>10:57</v>
+        <v>4:07</v>
       </c>
       <c r="H82" t="str">
-        <v>JavaJazzFest</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-17</v>
@@ -3532,10 +3532,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:14</v>
+        <v>5:00</v>
       </c>
       <c r="H83" t="str">
-        <v>Robert Grace</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B84" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-17</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:26</v>
+        <v>3:27</v>
       </c>
       <c r="H84" t="str">
-        <v>mgk</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-17</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>5:59</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>Victor Ray</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B86" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-17</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:46</v>
+        <v>10:57</v>
       </c>
       <c r="H86" t="str">
-        <v>Perrie</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B87" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-17</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:39</v>
+        <v>4:14</v>
       </c>
       <c r="H87" t="str">
-        <v>Michael Bolton</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-17</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:58</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Nothing But Thieves</v>
+        <v>mgk</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-17</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:26</v>
+        <v>5:59</v>
       </c>
       <c r="H89" t="str">
-        <v>Mimi Webb</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-17</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H90" t="str">
-        <v>Olivia Dean</v>
+        <v>Perrie</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-17</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>6:00</v>
+        <v>3:39</v>
       </c>
       <c r="H91" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-17</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:20</v>
+        <v>3:58</v>
       </c>
       <c r="H92" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-17</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:27</v>
+        <v>2:26</v>
       </c>
       <c r="H93" t="str">
-        <v>Mariah Carey</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-17</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H94" t="str">
-        <v>Netflix</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-17</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:29</v>
+        <v>6:00</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-17</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:59</v>
+        <v>4:20</v>
       </c>
       <c r="H96" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-17</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:51</v>
+        <v>4:27</v>
       </c>
       <c r="H97" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-17</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H98" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-17</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:41</v>
+        <v>3:29</v>
       </c>
       <c r="H99" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-17</v>
@@ -4178,10 +4178,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>7:03</v>
+        <v>2:59</v>
       </c>
       <c r="H100" t="str">
-        <v>Take That</v>
+        <v>mgk</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B101" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-17</v>
@@ -4216,10 +4216,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:37</v>
+        <v>2:51</v>
       </c>
       <c r="H101" t="str">
-        <v>Cliff Richard</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -474,13 +474,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES FEBRUARY 2026</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=llKawYldOdg</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>1:00:47</v>
+        <v>4:26</v>
       </c>
       <c r="H3" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES FEBRUARY 2026 - Purple Disco Machine</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:26</v>
+        <v>4:35</v>
       </c>
       <c r="H4" t="str">
-        <v>Neal Francis</v>
+        <v>mgk</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B5" t="str">
-        <v>4 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:35</v>
+        <v>4:11</v>
       </c>
       <c r="H5" t="str">
-        <v>mgk</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:11</v>
+        <v>3:01</v>
       </c>
       <c r="H6" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-17</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H7" t="str">
-        <v>The Vaccines</v>
+        <v>mgk</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-17</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:28</v>
+        <v>5:31</v>
       </c>
       <c r="H8" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-17</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:31</v>
+        <v>2:49</v>
       </c>
       <c r="H9" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-17</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:49</v>
+        <v>3:03</v>
       </c>
       <c r="H10" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-17</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-17</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H12" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-17</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H13" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-17</v>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H14" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-17</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:59</v>
+        <v>7:48</v>
       </c>
       <c r="H15" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-17</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>7:48</v>
+        <v>3:10</v>
       </c>
       <c r="H16" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-17</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:10</v>
+        <v>5:57</v>
       </c>
       <c r="H17" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-17</v>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:57</v>
+        <v>2:25</v>
       </c>
       <c r="H18" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-17</v>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:25</v>
+        <v>3:19</v>
       </c>
       <c r="H19" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-17</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H20" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-17</v>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:38</v>
+        <v>4:05</v>
       </c>
       <c r="H21" t="str">
-        <v>mgk</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-17</v>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:05</v>
+        <v>5:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-17</v>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:46</v>
+        <v>3:25</v>
       </c>
       <c r="H23" t="str">
-        <v>Jacob Collier</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-17</v>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:25</v>
+        <v>5:11</v>
       </c>
       <c r="H24" t="str">
-        <v>Victor Ray</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-17</v>
@@ -1328,10 +1328,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>5:11</v>
+        <v>2:55</v>
       </c>
       <c r="H25" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Warning</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-17</v>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:55</v>
+        <v>4:54</v>
       </c>
       <c r="H26" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-17</v>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:54</v>
+        <v>5:01</v>
       </c>
       <c r="H27" t="str">
-        <v>The Offspring</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-17</v>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:01</v>
+        <v>3:55</v>
       </c>
       <c r="H28" t="str">
-        <v>Caitlyn Smith</v>
+        <v>HAUSER</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-17</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H29" t="str">
-        <v>HAUSER</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-17</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H30" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-17</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:53</v>
+        <v>3:30</v>
       </c>
       <c r="H31" t="str">
-        <v>Ultra Records</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-17</v>
@@ -1594,10 +1594,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:30</v>
+        <v>3:37</v>
       </c>
       <c r="H32" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-17</v>
@@ -1632,10 +1632,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-17</v>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:10</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-17</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H35" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-17</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-17</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:21</v>
+        <v>6:58</v>
       </c>
       <c r="H37" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eric Church</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-17</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>6:58</v>
+        <v>3:29</v>
       </c>
       <c r="H38" t="str">
-        <v>Eric Church</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-17</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H39" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-17</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H40" t="str">
-        <v>Ally Salort</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-17</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:51</v>
+        <v>3:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Will Swinton</v>
+        <v>elijah woods</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-17</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H42" t="str">
-        <v>elijah woods</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-17</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H43" t="str">
-        <v>Jackson Dean</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-17</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H44" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-17</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H45" t="str">
-        <v>Neil Sedaka</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-17</v>
@@ -2126,10 +2126,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H46" t="str">
-        <v>Sofia Camara</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B47" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-17</v>
@@ -2164,10 +2164,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-17</v>
@@ -2202,10 +2202,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H48" t="str">
-        <v>Celine Dion</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-17</v>
@@ -2240,10 +2240,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H49" t="str">
-        <v>Bebe Rexha</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-17</v>
@@ -2278,10 +2278,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:29</v>
+        <v>2:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-17</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:32</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-17</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H52" t="str">
-        <v>Ingrid Andress</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B53" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-17</v>
@@ -2392,10 +2392,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H53" t="str">
-        <v>MusicByKnox</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B54" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-17</v>
@@ -2430,10 +2430,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H54" t="str">
-        <v>Ella Langley</v>
+        <v>Nickless</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-17</v>
@@ -2468,10 +2468,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H55" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-17</v>
@@ -2506,10 +2506,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:57</v>
+        <v>3:08</v>
       </c>
       <c r="H56" t="str">
-        <v>Caroline Jones</v>
+        <v>elijah woods</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-17</v>
@@ -2544,10 +2544,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H57" t="str">
-        <v>elijah woods</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-17</v>
@@ -2582,10 +2582,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:53</v>
+        <v>3:10</v>
       </c>
       <c r="H58" t="str">
-        <v>August Ponthier</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-17</v>
@@ -2620,10 +2620,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:10</v>
+        <v>2:58</v>
       </c>
       <c r="H59" t="str">
-        <v>Charli xcx</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-17</v>
@@ -2658,10 +2658,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:58</v>
+        <v>2:44</v>
       </c>
       <c r="H60" t="str">
-        <v>Caroline Jones</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-17</v>
@@ -2696,10 +2696,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:44</v>
+        <v>3:25</v>
       </c>
       <c r="H61" t="str">
-        <v>Leah Kate</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-17</v>
@@ -2734,10 +2734,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:25</v>
+        <v>4:08</v>
       </c>
       <c r="H62" t="str">
-        <v>Troye Sivan</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B63" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-17</v>
@@ -2772,10 +2772,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:08</v>
+        <v>3:09</v>
       </c>
       <c r="H63" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-17</v>
@@ -2810,10 +2810,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H64" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B65" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-17</v>
@@ -2848,10 +2848,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H65" t="str">
-        <v>The Happy Fits</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B66" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-17</v>
@@ -2886,10 +2886,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:02</v>
+        <v>4:20</v>
       </c>
       <c r="H66" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-17</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:20</v>
+        <v>4:09</v>
       </c>
       <c r="H67" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-17</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:09</v>
+        <v>4:34</v>
       </c>
       <c r="H68" t="str">
-        <v>Quinn XCII</v>
+        <v>We Three</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B69" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-17</v>
@@ -3000,10 +3000,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:34</v>
+        <v>3:29</v>
       </c>
       <c r="H69" t="str">
-        <v>We Three</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-17</v>
@@ -3038,10 +3038,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:29</v>
+        <v>2:51</v>
       </c>
       <c r="H70" t="str">
-        <v>A Thousand Horses</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-17</v>
@@ -3076,10 +3076,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B72" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-17</v>
@@ -3114,10 +3114,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H72" t="str">
-        <v>Constant Smiles</v>
+        <v>P!NK</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-17</v>
@@ -3152,10 +3152,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H73" t="str">
-        <v>P!NK</v>
+        <v>Bazzi</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B74" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-17</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:33</v>
+        <v>4:18</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-17</v>
@@ -3228,7 +3228,7 @@
         <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:18</v>
+        <v>2:08</v>
       </c>
       <c r="H75" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-17</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:08</v>
+        <v>3:56</v>
       </c>
       <c r="H76" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>bleachers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-17</v>
@@ -3304,10 +3304,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:56</v>
+        <v>3:27</v>
       </c>
       <c r="H77" t="str">
-        <v>bleachers</v>
+        <v>The Academic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-17</v>
@@ -3342,10 +3342,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>2:39</v>
       </c>
       <c r="H78" t="str">
-        <v>The Academic</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-17</v>
@@ -3380,10 +3380,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:39</v>
+        <v>3:54</v>
       </c>
       <c r="H79" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B80" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-17</v>
@@ -3418,10 +3418,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:54</v>
+        <v>3:47</v>
       </c>
       <c r="H80" t="str">
-        <v>Michael Bolton</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B81" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-17</v>
@@ -3456,10 +3456,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>4:07</v>
       </c>
       <c r="H81" t="str">
-        <v>Caroline Jones</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-17</v>
@@ -3494,10 +3494,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:07</v>
+        <v>5:00</v>
       </c>
       <c r="H82" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B83" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-17</v>
@@ -3532,10 +3532,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:00</v>
+        <v>3:27</v>
       </c>
       <c r="H83" t="str">
-        <v>Michael Bolton</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-17</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H84" t="str">
-        <v>Little Big Town</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-17</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>10:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B86" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-17</v>
@@ -3646,10 +3646,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>10:57</v>
+        <v>4:14</v>
       </c>
       <c r="H86" t="str">
-        <v>JavaJazzFest</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-17</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:14</v>
+        <v>3:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Robert Grace</v>
+        <v>mgk</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-17</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>5:59</v>
       </c>
       <c r="H88" t="str">
-        <v>mgk</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-17</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:59</v>
+        <v>2:46</v>
       </c>
       <c r="H89" t="str">
-        <v>Victor Ray</v>
+        <v>Perrie</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-17</v>
@@ -3798,10 +3798,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:46</v>
+        <v>3:39</v>
       </c>
       <c r="H90" t="str">
-        <v>Perrie</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-17</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:39</v>
+        <v>3:58</v>
       </c>
       <c r="H91" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-17</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:58</v>
+        <v>2:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-17</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:26</v>
+        <v>3:04</v>
       </c>
       <c r="H93" t="str">
-        <v>Mimi Webb</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-17</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:04</v>
+        <v>6:00</v>
       </c>
       <c r="H94" t="str">
-        <v>Olivia Dean</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-17</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>6:00</v>
+        <v>4:20</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-17</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:20</v>
+        <v>4:27</v>
       </c>
       <c r="H96" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-17</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H97" t="str">
-        <v>Mariah Carey</v>
+        <v>Netflix</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-17</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H98" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-17</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H99" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B100" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-17</v>
@@ -4178,10 +4178,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>mgk</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-17</v>
@@ -4216,10 +4216,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:51</v>
+        <v>4:13</v>
       </c>
       <c r="H101" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="102">
@@ -4312,13 +4312,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Be Her</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-17</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:37</v>
+        <v>3:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L104" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-17</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G105" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H105" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L105" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-17</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G106" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H106" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L106" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-17</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H107" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L107" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Casual Lady</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-17</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Casual Lady - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G108" t="str">
-        <v>3:14</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>flowerovlove</v>
+        <v>CORTIS</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L108" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-17</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Trying Times</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:40</v>
+        <v>3:14</v>
       </c>
       <c r="H109" t="str">
-        <v>James Blake</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L109" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-17</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G110" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H110" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L110" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-17</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H111" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L111" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-17</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H112" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L112" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-17</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G113" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H113" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L113" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-17</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H114" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L114" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-17</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H115" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L115" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-17</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H116" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L116" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-17</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H117" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L117" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-17</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G118" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L118" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-17</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G119" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H119" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L119" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-17</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G120" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H120" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L120" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-17</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H121" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L121" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-17</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H122" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L122" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-17</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G123" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H123" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L123" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-17</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H124" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L124" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-17</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G125" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H125" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L125" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-17</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G126" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H126" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L126" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-17</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H127" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L127" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-17</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G128" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H128" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L128" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-17</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H129" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L129" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-17</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H130" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L130" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-17</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L131" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-17</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G132" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H132" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L132" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-17</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G133" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H133" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L133" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-17</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L134" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-17</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G135" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H135" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L135" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-17</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H136" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L136" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-17</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H137" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L137" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-17</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H138" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L138" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-17</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H139" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L139" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-17</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G140" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H140" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L140" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-17</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H141" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L141" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-17</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H142" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L142" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-17</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H143" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L143" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-17</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H144" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L144" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-17</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G145" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L145" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-17</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H146" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L146" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-17</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H147" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L147" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-17</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G148" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H148" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L148" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-17</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H149" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L149" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-17</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H150" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L150" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-17</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G151" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H151" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L151" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-17</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G152" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H152" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L152" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-17</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H153" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L153" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-17</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G154" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H154" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L154" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-17</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G155" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H155" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L155" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-17</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G156" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H156" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L156" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-17</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H157" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L157" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-17</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H158" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L158" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-17</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H159" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L159" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-17</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H160" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L160" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-17</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H161" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L161" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-17</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H162" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L162" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-17</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H163" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L163" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-17</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H164" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L164" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-17</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G165" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H165" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L165" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-17</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G166" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H166" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L166" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-17</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G167" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H167" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L167" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-17</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H168" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L168" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-17</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L169" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-17</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H170" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L170" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-17</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H171" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L171" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-17</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H172" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L172" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-17</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L173" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-17</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H174" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L174" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-17</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G175" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H175" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L175" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-17</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H176" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L176" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-17</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G177" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H177" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L177" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-17</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H178" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L178" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-17</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H179" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L179" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-17</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H180" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L180" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-17</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G181" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H181" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L181" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-17</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G182" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L182" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-17</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H183" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L183" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-17</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G184" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H184" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L184" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-17</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G185" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H185" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L185" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-17</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H186" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L186" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-17</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H187" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L187" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-17</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H188" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L188" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-17</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H189" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L189" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-17</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G190" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H190" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L190" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-17</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G191" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L191" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-17</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H192" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L192" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-17</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G193" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H193" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L193" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-17</v>
@@ -7747,68 +7747,106 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G194" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H194" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L194" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G195" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D195" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
+      <c r="D196" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G196" t="str">
         <v>3:17</v>
       </c>
-      <c r="H195" t="str">
+      <c r="H196" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K195" t="str">
+      <c r="K196" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L195" t="str">
+      <c r="L196" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,19 +439,19 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,19 +477,19 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,19 +515,19 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:11</v>
@@ -2833,19 +2833,19 @@
         <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:02</v>
@@ -2871,19 +2871,19 @@
         <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:20</v>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>4:14</v>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E196" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-18</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:11</v>
+        <v>2:09</v>
       </c>
       <c r="H5" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lola Young</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-18</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v>4:11</v>
       </c>
       <c r="H6" t="str">
-        <v>The Vaccines</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-18</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H7" t="str">
-        <v>mgk</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-18</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H8" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-18</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H9" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-18</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H10" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-18</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H11" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-18</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H12" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-18</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H13" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-18</v>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H14" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-18</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H15" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B16" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-18</v>
@@ -986,10 +986,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H16" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B17" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-18</v>
@@ -1024,10 +1024,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H17" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-18</v>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H18" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-18</v>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H19" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-18</v>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H20" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-18</v>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H21" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-18</v>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-18</v>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-18</v>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H24" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-18</v>
@@ -1328,10 +1328,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H25" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-18</v>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H26" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-18</v>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H27" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-18</v>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H28" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-18</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H29" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-18</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>11 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H30" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-18</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-18</v>
@@ -1594,10 +1594,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H32" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-18</v>
@@ -1632,10 +1632,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-18</v>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H34" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-18</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H35" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-18</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H36" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-18</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-18</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H38" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-18</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H39" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-18</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-18</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H41" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-18</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H42" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-18</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H43" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-18</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H44" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-18</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H45" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-18</v>
@@ -2126,10 +2126,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H46" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-18</v>
@@ -2164,10 +2164,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H47" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B48" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-18</v>
@@ -2202,10 +2202,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H48" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-18</v>
@@ -2240,10 +2240,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H49" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-18</v>
@@ -2278,10 +2278,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H50" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-18</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-18</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-18</v>
@@ -2392,10 +2392,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H53" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-18</v>
@@ -2430,10 +2430,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H54" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B55" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-18</v>
@@ -2468,10 +2468,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H55" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-18</v>
@@ -2506,10 +2506,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H56" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-18</v>
@@ -2544,10 +2544,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H57" t="str">
-        <v>August Ponthier</v>
+        <v>elijah woods</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-18</v>
@@ -2582,10 +2582,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:10</v>
+        <v>3:53</v>
       </c>
       <c r="H58" t="str">
-        <v>Charli xcx</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-18</v>
@@ -2620,10 +2620,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:58</v>
+        <v>3:10</v>
       </c>
       <c r="H59" t="str">
-        <v>Caroline Jones</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-18</v>
@@ -2658,10 +2658,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:44</v>
+        <v>2:58</v>
       </c>
       <c r="H60" t="str">
-        <v>Leah Kate</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-18</v>
@@ -2696,10 +2696,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:25</v>
+        <v>2:44</v>
       </c>
       <c r="H61" t="str">
-        <v>Troye Sivan</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-18</v>
@@ -2734,10 +2734,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:08</v>
+        <v>3:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-18</v>
@@ -2772,10 +2772,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:09</v>
+        <v>4:08</v>
       </c>
       <c r="H63" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B64" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-18</v>
@@ -2810,10 +2810,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:11</v>
+        <v>3:09</v>
       </c>
       <c r="H64" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-18</v>
@@ -2848,10 +2848,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:02</v>
+        <v>3:11</v>
       </c>
       <c r="H65" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B66" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-18</v>
@@ -2886,10 +2886,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:20</v>
+        <v>3:02</v>
       </c>
       <c r="H66" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B67" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-18</v>
@@ -2924,10 +2924,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:09</v>
+        <v>4:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Quinn XCII</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B68" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-18</v>
@@ -2962,10 +2962,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:34</v>
+        <v>4:09</v>
       </c>
       <c r="H68" t="str">
-        <v>We Three</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B69" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-18</v>
@@ -3000,10 +3000,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:29</v>
+        <v>4:34</v>
       </c>
       <c r="H69" t="str">
-        <v>A Thousand Horses</v>
+        <v>We Three</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B70" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-18</v>
@@ -3038,10 +3038,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H70" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-18</v>
@@ -3076,10 +3076,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:56</v>
+        <v>2:51</v>
       </c>
       <c r="H71" t="str">
-        <v>Constant Smiles</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-18</v>
@@ -3114,10 +3114,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:25</v>
+        <v>2:56</v>
       </c>
       <c r="H72" t="str">
-        <v>P!NK</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B73" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-18</v>
@@ -3152,10 +3152,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:33</v>
+        <v>3:25</v>
       </c>
       <c r="H73" t="str">
-        <v>Bazzi</v>
+        <v>P!NK</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-18</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:18</v>
+        <v>2:33</v>
       </c>
       <c r="H74" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bazzi</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-18</v>
@@ -3228,7 +3228,7 @@
         <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:08</v>
+        <v>4:18</v>
       </c>
       <c r="H75" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B76" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-18</v>
@@ -3266,10 +3266,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:56</v>
+        <v>2:08</v>
       </c>
       <c r="H76" t="str">
-        <v>bleachers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-18</v>
@@ -3304,10 +3304,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:27</v>
+        <v>3:56</v>
       </c>
       <c r="H77" t="str">
-        <v>The Academic</v>
+        <v>bleachers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-18</v>
@@ -3342,10 +3342,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:39</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Academic</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-18</v>
@@ -3380,10 +3380,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:54</v>
+        <v>2:39</v>
       </c>
       <c r="H79" t="str">
-        <v>Michael Bolton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-18</v>
@@ -3418,10 +3418,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:47</v>
+        <v>3:54</v>
       </c>
       <c r="H80" t="str">
-        <v>Caroline Jones</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B81" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-18</v>
@@ -3456,10 +3456,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:07</v>
+        <v>3:47</v>
       </c>
       <c r="H81" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B82" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-18</v>
@@ -3494,10 +3494,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:00</v>
+        <v>4:07</v>
       </c>
       <c r="H82" t="str">
-        <v>Michael Bolton</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-18</v>
@@ -3532,10 +3532,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:27</v>
+        <v>5:00</v>
       </c>
       <c r="H83" t="str">
-        <v>Little Big Town</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B84" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-18</v>
@@ -3570,10 +3570,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H84" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-18</v>
@@ -3608,10 +3608,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>10:57</v>
+        <v>3:25</v>
       </c>
       <c r="H85" t="str">
-        <v>JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B86" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-18</v>
@@ -3646,10 +3646,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:14</v>
+        <v>10:57</v>
       </c>
       <c r="H86" t="str">
-        <v>Robert Grace</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-18</v>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>4:14</v>
       </c>
       <c r="H87" t="str">
-        <v>mgk</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-18</v>
@@ -3722,10 +3722,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:59</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Victor Ray</v>
+        <v>mgk</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-18</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:46</v>
+        <v>5:59</v>
       </c>
       <c r="H89" t="str">
-        <v>Perrie</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-18</v>
@@ -3798,10 +3798,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:39</v>
+        <v>2:46</v>
       </c>
       <c r="H90" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-18</v>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:58</v>
+        <v>3:39</v>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-18</v>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:26</v>
+        <v>3:58</v>
       </c>
       <c r="H92" t="str">
-        <v>Mimi Webb</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-18</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:04</v>
+        <v>2:26</v>
       </c>
       <c r="H93" t="str">
-        <v>Olivia Dean</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-18</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H94" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-18</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-18</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H96" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-18</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H97" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-18</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H98" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-18</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H99" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-18</v>
@@ -4178,10 +4178,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H100" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B101" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-18</v>
@@ -4216,10 +4216,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H101" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -1731,7 +1731,7 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:17</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:21</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -1807,7 +1807,7 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>6:58</v>
@@ -1845,7 +1845,7 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:29</v>
@@ -1883,7 +1883,7 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:14</v>
@@ -1921,7 +1921,7 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:51</v>
@@ -1959,7 +1959,7 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:10</v>
@@ -1997,7 +1997,7 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:26</v>
@@ -2035,7 +2035,7 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:51</v>
@@ -2073,7 +2073,7 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:26</v>
@@ -2111,7 +2111,7 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:06</v>
@@ -2149,7 +2149,7 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:04</v>
@@ -2187,7 +2187,7 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:03</v>
@@ -2225,7 +2225,7 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:38</v>
@@ -2263,7 +2263,7 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:29</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:32</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -2339,7 +2339,7 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:32</v>
@@ -2377,7 +2377,7 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:51</v>
@@ -2415,7 +2415,7 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:38</v>
@@ -2453,7 +2453,7 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:26</v>
@@ -2491,7 +2491,7 @@
         <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:57</v>
@@ -2529,7 +2529,7 @@
         <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:08</v>
@@ -2567,7 +2567,7 @@
         <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:53</v>
@@ -2605,7 +2605,7 @@
         <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:10</v>
@@ -2643,7 +2643,7 @@
         <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:58</v>
@@ -2681,7 +2681,7 @@
         <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:44</v>
@@ -2719,7 +2719,7 @@
         <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:25</v>
@@ -2757,7 +2757,7 @@
         <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>4:08</v>
@@ -3175,7 +3175,7 @@
         <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:33</v>
@@ -3555,7 +3555,7 @@
         <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:27</v>
@@ -3593,7 +3593,7 @@
         <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:25</v>
@@ -3897,7 +3897,7 @@
         <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>2:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:10</v>
@@ -1693,7 +1693,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:06</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -1617,7 +1617,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:37</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -3099,7 +3099,7 @@
         <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>2:56</v>
@@ -3137,7 +3137,7 @@
         <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B73" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:25</v>
@@ -3517,7 +3517,7 @@
         <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>5:00</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -629,7 +629,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:01</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -3061,7 +3061,7 @@
         <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>2:51</v>
@@ -4011,7 +4011,7 @@
         <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>4:20</v>
@@ -4125,7 +4125,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:29</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -933,7 +933,7 @@
         <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:59</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -3973,7 +3973,7 @@
         <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>6:00</v>
@@ -4087,7 +4087,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:26</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -895,7 +895,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:59</v>
@@ -1465,7 +1465,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:55</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -3745,7 +3745,7 @@
         <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>5:59</v>
@@ -3821,7 +3821,7 @@
         <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:39</v>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B92" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:58</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -1427,7 +1427,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>5:01</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -3023,7 +3023,7 @@
         <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:29</v>
@@ -3479,7 +3479,7 @@
         <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B82" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>4:07</v>
@@ -4201,7 +4201,7 @@
         <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>2:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -553,7 +553,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:09</v>
@@ -705,7 +705,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>5:31</v>
@@ -857,7 +857,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:41</v>
@@ -1313,7 +1313,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>5:11</v>
@@ -1351,7 +1351,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:55</v>
@@ -1389,7 +1389,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:54</v>
@@ -1541,7 +1541,7 @@
         <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:53</v>
@@ -3441,7 +3441,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:47</v>
@@ -3783,7 +3783,7 @@
         <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:46</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-18</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H102" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L102" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="103">
@@ -4502,13 +4502,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-18</v>
@@ -4517,25 +4517,25 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G109" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H109" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L109" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="110">
@@ -4578,13 +4578,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Let Me</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-18</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Let Me - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:51</v>
+        <v>3:14</v>
       </c>
       <c r="H111" t="str">
-        <v>Victoria Monét</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L111" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-18</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H112" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L112" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-18</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H113" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L113" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-18</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G114" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H114" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L114" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-18</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H115" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L115" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-18</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H116" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L116" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-18</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H117" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L117" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-18</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H118" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L118" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-18</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G119" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L119" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-18</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G120" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H120" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L120" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-18</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G121" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H121" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L121" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-18</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H122" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L122" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-18</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H123" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L123" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-18</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G124" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H124" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L124" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-18</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H125" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L125" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-18</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G126" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H126" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L126" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-18</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G127" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H127" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L127" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-18</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H128" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L128" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-18</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G129" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H129" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L129" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-18</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H130" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L130" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-18</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H131" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L131" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-18</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H132" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L132" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-18</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G133" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H133" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L133" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-18</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H134" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L134" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-18</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H135" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L135" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-18</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G136" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H136" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L136" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-18</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H137" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L137" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-18</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H138" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L138" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-18</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H139" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L139" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-18</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H140" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L140" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-18</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G141" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H141" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L141" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-18</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H142" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L142" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-18</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H143" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L143" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-18</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H144" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L144" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-18</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H145" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L145" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-18</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G146" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H146" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L146" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-18</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H147" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L147" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-18</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H148" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L148" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-18</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G149" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H149" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L149" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-18</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H150" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L150" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-18</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H151" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L151" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-18</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G152" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H152" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L152" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-18</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G153" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H153" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L153" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-18</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H154" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L154" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-18</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G155" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H155" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L155" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-18</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G156" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H156" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L156" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-18</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G157" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H157" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L157" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-18</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L158" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-18</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H159" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L159" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-18</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H160" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L160" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-18</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H161" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L161" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-18</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H162" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L162" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-18</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H163" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L163" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-18</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H164" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L164" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-18</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H165" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L165" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-18</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G166" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H166" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L166" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-18</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G167" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H167" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L167" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-18</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G168" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H168" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L168" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-18</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H169" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L169" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-18</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L170" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-18</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L171" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-18</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H172" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L172" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-18</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H173" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L173" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-18</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H174" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L174" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-18</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H175" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L175" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-18</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G176" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L176" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-18</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H177" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L177" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-18</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G178" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L178" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-18</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L179" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-18</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H180" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L180" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-18</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H181" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L181" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-18</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H182" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L182" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-18</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G183" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H183" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L183" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-18</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H184" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L184" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-18</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G185" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H185" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L185" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-18</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G186" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H186" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L186" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-18</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H187" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L187" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-18</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H188" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L188" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-18</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H189" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L189" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-18</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H190" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L190" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-18</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H191" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L191" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-18</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G192" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H192" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L192" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-18</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H193" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L193" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-18</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G194" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L194" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-18</v>
@@ -7785,68 +7785,106 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G195" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H195" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L195" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D196" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
+      <c r="D197" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G196" t="str">
+      <c r="G197" t="str">
         <v>3:17</v>
       </c>
-      <c r="H196" t="str">
+      <c r="H197" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K196" t="str">
+      <c r="K197" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L196" t="str">
+      <c r="L197" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -515,7 +515,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:35</v>
@@ -591,7 +591,7 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:11</v>
@@ -667,7 +667,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:28</v>
@@ -781,7 +781,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:03</v>
@@ -819,7 +819,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:59</v>
@@ -1085,7 +1085,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:25</v>
@@ -1123,7 +1123,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:19</v>
@@ -1161,7 +1161,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:38</v>
@@ -1199,7 +1199,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>4:05</v>
@@ -1237,7 +1237,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>5:46</v>
@@ -1275,7 +1275,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:25</v>
@@ -1579,7 +1579,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:30</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -2985,7 +2985,7 @@
         <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>4:34</v>
@@ -3327,7 +3327,7 @@
         <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:27</v>
@@ -3365,7 +3365,7 @@
         <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>2:39</v>
@@ -3403,7 +3403,7 @@
         <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:54</v>
@@ -3707,7 +3707,7 @@
         <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:26</v>
@@ -3935,7 +3935,7 @@
         <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:04</v>
@@ -4163,7 +4163,7 @@
         <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -477,7 +477,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:26</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -3289,7 +3289,7 @@
         <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:11</v>
@@ -743,7 +743,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>2:49</v>
@@ -1047,7 +1047,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>5:57</v>
@@ -1503,7 +1503,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:43</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -4049,7 +4049,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:27</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="52">
@@ -3213,7 +3213,7 @@
         <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>4:18</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -3894,13 +3894,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=b_RNVL7cV6M</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-18</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:26</v>
+        <v>3:04</v>
       </c>
       <c r="H93" t="str">
-        <v>Mimi Webb</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Mimi Webb - Eyes Closed (Official Lyric Video) - Mimi Webb</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-18</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:04</v>
+        <v>6:00</v>
       </c>
       <c r="H94" t="str">
-        <v>Olivia Dean</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-18</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>6:00</v>
+        <v>4:20</v>
       </c>
       <c r="H95" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-18</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:20</v>
+        <v>4:27</v>
       </c>
       <c r="H96" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B97" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-18</v>
@@ -4064,10 +4064,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H97" t="str">
-        <v>Mariah Carey</v>
+        <v>Netflix</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-18</v>
@@ -4102,10 +4102,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H98" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-18</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H99" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B100" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-18</v>
@@ -4178,10 +4178,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>mgk</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-18</v>
@@ -4216,10 +4216,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:51</v>
+        <v>4:13</v>
       </c>
       <c r="H101" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:10</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="38">
@@ -2947,7 +2947,7 @@
         <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:09</v>
@@ -3251,7 +3251,7 @@
         <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -436,25 +436,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:11</v>
+        <v>3:43</v>
       </c>
       <c r="H2" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:26</v>
+        <v>2:58</v>
       </c>
       <c r="H3" t="str">
-        <v>Neal Francis</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:35</v>
+        <v>4:13</v>
       </c>
       <c r="H4" t="str">
-        <v>mgk</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:09</v>
+        <v>5:48</v>
       </c>
       <c r="H5" t="str">
-        <v>Lola Young</v>
+        <v>U2</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:11</v>
+        <v>3:55</v>
       </c>
       <c r="H6" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lawrence</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:01</v>
+        <v>5:24</v>
       </c>
       <c r="H7" t="str">
-        <v>The Vaccines</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:28</v>
+        <v>4:59</v>
       </c>
       <c r="H8" t="str">
-        <v>mgk</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,30 +697,30 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:31</v>
+        <v>2:10</v>
       </c>
       <c r="H9" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:49</v>
+        <v>3:11</v>
       </c>
       <c r="H10" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:03</v>
+        <v>4:26</v>
       </c>
       <c r="H11" t="str">
-        <v>Michael Bolton</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:59</v>
+        <v>4:35</v>
       </c>
       <c r="H12" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>mgk</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:41</v>
+        <v>2:09</v>
       </c>
       <c r="H13" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Lola Young</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>4:11</v>
       </c>
       <c r="H14" t="str">
-        <v>ENHYPEN</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:59</v>
+        <v>3:01</v>
       </c>
       <c r="H15" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>7:48</v>
+        <v>3:28</v>
       </c>
       <c r="H16" t="str">
-        <v>The Doobie Brothers</v>
+        <v>mgk</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:10</v>
+        <v>5:31</v>
       </c>
       <c r="H17" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:57</v>
+        <v>2:49</v>
       </c>
       <c r="H18" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Mýa</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:25</v>
+        <v>3:03</v>
       </c>
       <c r="H19" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:19</v>
+        <v>2:59</v>
       </c>
       <c r="H20" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:38</v>
+        <v>2:41</v>
       </c>
       <c r="H21" t="str">
-        <v>mgk</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H22" t="str">
-        <v>Dermot Kennedy</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>5:46</v>
+        <v>3:59</v>
       </c>
       <c r="H23" t="str">
-        <v>Jacob Collier</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:25</v>
+        <v>7:48</v>
       </c>
       <c r="H24" t="str">
-        <v>Victor Ray</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>5:11</v>
+        <v>3:10</v>
       </c>
       <c r="H25" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:55</v>
+        <v>5:57</v>
       </c>
       <c r="H26" t="str">
-        <v>The Warning</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:54</v>
+        <v>2:25</v>
       </c>
       <c r="H27" t="str">
-        <v>The Offspring</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>5:01</v>
+        <v>3:19</v>
       </c>
       <c r="H28" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:55</v>
+        <v>3:38</v>
       </c>
       <c r="H29" t="str">
-        <v>HAUSER</v>
+        <v>mgk</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:43</v>
+        <v>4:05</v>
       </c>
       <c r="H30" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B31" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>12 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:53</v>
+        <v>5:46</v>
       </c>
       <c r="H31" t="str">
-        <v>Ultra Records</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:30</v>
+        <v>3:25</v>
       </c>
       <c r="H32" t="str">
-        <v>Anja Kotar</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:37</v>
+        <v>5:11</v>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bolton</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:10</v>
+        <v>2:55</v>
       </c>
       <c r="H34" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Warning</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>4:54</v>
       </c>
       <c r="H35" t="str">
-        <v>Alan Walker</v>
+        <v>The Offspring</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B36" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>5:01</v>
       </c>
       <c r="H36" t="str">
-        <v>Bruno Mars</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:21</v>
+        <v>3:55</v>
       </c>
       <c r="H37" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>HAUSER</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B38" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>6:58</v>
+        <v>3:43</v>
       </c>
       <c r="H38" t="str">
-        <v>Eric Church</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:29</v>
+        <v>2:53</v>
       </c>
       <c r="H39" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,21 +1875,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:14</v>
+        <v>3:30</v>
       </c>
       <c r="H40" t="str">
-        <v>Ally Salort</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,21 +1913,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:51</v>
+        <v>3:37</v>
       </c>
       <c r="H41" t="str">
-        <v>Will Swinton</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:10</v>
+        <v>4:10</v>
       </c>
       <c r="H42" t="str">
-        <v>elijah woods</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H43" t="str">
-        <v>Jackson Dean</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H44" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H45" t="str">
-        <v>Neil Sedaka</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:06</v>
+        <v>6:58</v>
       </c>
       <c r="H46" t="str">
-        <v>Sofia Camara</v>
+        <v>Eric Church</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H47" t="str">
-        <v>Russell Dickerson</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:03</v>
+        <v>3:14</v>
       </c>
       <c r="H48" t="str">
-        <v>Celine Dion</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:38</v>
+        <v>3:51</v>
       </c>
       <c r="H49" t="str">
-        <v>Bebe Rexha</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:29</v>
+        <v>3:10</v>
       </c>
       <c r="H50" t="str">
-        <v>Caroline Jones</v>
+        <v>elijah woods</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:32</v>
+        <v>3:26</v>
       </c>
       <c r="H51" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,21 +2331,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B52" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2354,10 +2354,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H52" t="str">
-        <v>Ingrid Andress</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B53" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H53" t="str">
-        <v>MusicByKnox</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,21 +2407,21 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2430,10 +2430,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:38</v>
+        <v>3:06</v>
       </c>
       <c r="H54" t="str">
-        <v>Ella Langley</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H55" t="str">
-        <v>Nickless</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B56" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H56" t="str">
-        <v>Caroline Jones</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:08</v>
+        <v>2:38</v>
       </c>
       <c r="H57" t="str">
-        <v>elijah woods</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:53</v>
+        <v>3:29</v>
       </c>
       <c r="H58" t="str">
-        <v>August Ponthier</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:10</v>
+        <v>2:32</v>
       </c>
       <c r="H59" t="str">
-        <v>Charli xcx</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B60" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:58</v>
+        <v>3:32</v>
       </c>
       <c r="H60" t="str">
-        <v>Caroline Jones</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:44</v>
+        <v>2:51</v>
       </c>
       <c r="H61" t="str">
-        <v>Leah Kate</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:25</v>
+        <v>3:38</v>
       </c>
       <c r="H62" t="str">
-        <v>Troye Sivan</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B63" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:08</v>
+        <v>3:26</v>
       </c>
       <c r="H63" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Nickless</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:09</v>
+        <v>3:57</v>
       </c>
       <c r="H64" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:11</v>
+        <v>3:08</v>
       </c>
       <c r="H65" t="str">
-        <v>The Happy Fits</v>
+        <v>elijah woods</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:02</v>
+        <v>3:53</v>
       </c>
       <c r="H66" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:20</v>
+        <v>3:10</v>
       </c>
       <c r="H67" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:09</v>
+        <v>2:58</v>
       </c>
       <c r="H68" t="str">
-        <v>Quinn XCII</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:34</v>
+        <v>2:44</v>
       </c>
       <c r="H69" t="str">
-        <v>We Three</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:29</v>
+        <v>3:25</v>
       </c>
       <c r="H70" t="str">
-        <v>A Thousand Horses</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:51</v>
+        <v>4:08</v>
       </c>
       <c r="H71" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B72" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:56</v>
+        <v>3:09</v>
       </c>
       <c r="H72" t="str">
-        <v>Constant Smiles</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H73" t="str">
-        <v>P!NK</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B74" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:33</v>
+        <v>3:02</v>
       </c>
       <c r="H74" t="str">
-        <v>Bazzi</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,30 +3205,30 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B75" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:18</v>
+        <v>4:20</v>
       </c>
       <c r="H75" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B76" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:08</v>
+        <v>4:09</v>
       </c>
       <c r="H76" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B77" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:56</v>
+        <v>4:34</v>
       </c>
       <c r="H77" t="str">
-        <v>bleachers</v>
+        <v>We Three</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B78" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>3:29</v>
       </c>
       <c r="H78" t="str">
-        <v>The Academic</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:39</v>
+        <v>2:51</v>
       </c>
       <c r="H79" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:54</v>
+        <v>2:56</v>
       </c>
       <c r="H80" t="str">
-        <v>Michael Bolton</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B81" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H81" t="str">
-        <v>Caroline Jones</v>
+        <v>P!NK</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:07</v>
+        <v>2:33</v>
       </c>
       <c r="H82" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Bazzi</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B83" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:00</v>
+        <v>4:18</v>
       </c>
       <c r="H83" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B84" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:27</v>
+        <v>2:08</v>
       </c>
       <c r="H84" t="str">
-        <v>Little Big Town</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:25</v>
+        <v>3:56</v>
       </c>
       <c r="H85" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>bleachers</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>10:57</v>
+        <v>3:27</v>
       </c>
       <c r="H86" t="str">
-        <v>JavaJazzFest</v>
+        <v>The Academic</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:14</v>
+        <v>2:39</v>
       </c>
       <c r="H87" t="str">
-        <v>Robert Grace</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:54</v>
       </c>
       <c r="H88" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:59</v>
+        <v>3:47</v>
       </c>
       <c r="H89" t="str">
-        <v>Victor Ray</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:46</v>
+        <v>4:07</v>
       </c>
       <c r="H90" t="str">
-        <v>Perrie</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,30 +3813,30 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:39</v>
+        <v>5:00</v>
       </c>
       <c r="H91" t="str">
         <v>Michael Bolton</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:58</v>
+        <v>3:27</v>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H93" t="str">
-        <v>Olivia Dean</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>6:00</v>
+        <v>10:57</v>
       </c>
       <c r="H94" t="str">
-        <v>Taylor Swift</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:20</v>
+        <v>4:14</v>
       </c>
       <c r="H95" t="str">
-        <v>Michael Bolton</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H96" t="str">
-        <v>Mariah Carey</v>
+        <v>mgk</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:26</v>
+        <v>5:59</v>
       </c>
       <c r="H97" t="str">
-        <v>Netflix</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:29</v>
+        <v>2:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Michael Bolton</v>
+        <v>Perrie</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:59</v>
+        <v>3:39</v>
       </c>
       <c r="H99" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>3:58</v>
       </c>
       <c r="H100" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Nothing But Thieves - Particles (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B101" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:13</v>
+        <v>3:04</v>
       </c>
       <c r="H101" t="str">
-        <v>Michael Bolton</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E197" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -1275,7 +1275,7 @@
         <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>7:48</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -3099,7 +3099,7 @@
         <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B72" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:09</v>
@@ -3935,7 +3935,7 @@
         <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B94" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>10:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -2035,7 +2035,7 @@
         <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>3:17</v>
@@ -2073,7 +2073,7 @@
         <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:21</v>
@@ -2111,7 +2111,7 @@
         <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>6:58</v>
@@ -2149,7 +2149,7 @@
         <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:29</v>
@@ -2187,7 +2187,7 @@
         <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:14</v>
@@ -2225,7 +2225,7 @@
         <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:51</v>
@@ -2263,7 +2263,7 @@
         <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:10</v>
@@ -2301,7 +2301,7 @@
         <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:26</v>
@@ -2339,7 +2339,7 @@
         <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:51</v>
@@ -2377,7 +2377,7 @@
         <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:26</v>
@@ -2415,7 +2415,7 @@
         <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:06</v>
@@ -2453,7 +2453,7 @@
         <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:04</v>
@@ -2491,7 +2491,7 @@
         <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B56" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:03</v>
@@ -2529,7 +2529,7 @@
         <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:38</v>
@@ -2567,7 +2567,7 @@
         <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:29</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:32</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">
@@ -2643,7 +2643,7 @@
         <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B60" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:32</v>
@@ -2681,7 +2681,7 @@
         <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:51</v>
@@ -2719,7 +2719,7 @@
         <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:38</v>
@@ -2757,7 +2757,7 @@
         <v>Nickless - As I Am</v>
       </c>
       <c r="B63" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:26</v>
@@ -2795,7 +2795,7 @@
         <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:57</v>
@@ -2833,7 +2833,7 @@
         <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:08</v>
@@ -2871,7 +2871,7 @@
         <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:53</v>
@@ -2909,7 +2909,7 @@
         <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:10</v>
@@ -2947,7 +2947,7 @@
         <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>2:58</v>
@@ -2985,7 +2985,7 @@
         <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:44</v>
@@ -3023,7 +3023,7 @@
         <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:25</v>
@@ -3061,7 +3061,7 @@
         <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:08</v>
@@ -3479,7 +3479,7 @@
         <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:33</v>
@@ -3859,7 +3859,7 @@
         <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:27</v>
@@ -3897,7 +3897,7 @@
         <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:25</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -1959,7 +1959,7 @@
         <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>4:10</v>
@@ -1997,7 +1997,7 @@
         <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:06</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -1921,7 +1921,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:37</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - BFTB Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -3403,7 +3403,7 @@
         <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>2:56</v>
@@ -3441,7 +3441,7 @@
         <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B81" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:25</v>
@@ -3821,7 +3821,7 @@
         <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>5:00</v>
@@ -6326,13 +6326,13 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>be the girl!</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-19</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>the apple tree under the sea</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>5:33</v>
+        <v>3:33</v>
       </c>
       <c r="H157" t="str">
-        <v>hemlocke springs</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L157" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-19</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:33</v>
+        <v>3:40</v>
       </c>
       <c r="H158" t="str">
-        <v>Erin LeCount</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L158" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>ARCADE</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-19</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:40</v>
+        <v>2:52</v>
       </c>
       <c r="H159" t="str">
-        <v>Kid Sistr</v>
+        <v>Deb Never</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L159" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>ARCADE</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-19</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>ARCADE - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H160" t="str">
-        <v>Deb Never</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L160" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Girls Just Wanna</v>
+        <v>you special.</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-19</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Girlhood - EP</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:16</v>
+        <v>2:08</v>
       </c>
       <c r="H161" t="str">
-        <v>Morgan St. Jean</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L161" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>you special.</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-19</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>you special. - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:08</v>
+        <v>3:38</v>
       </c>
       <c r="H162" t="str">
-        <v>YFN Lucci</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L162" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Bass Dhol</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-19</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H163" t="str">
-        <v>Ahadadream</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L163" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-19</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H164" t="str">
-        <v>Charles Kelley</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L164" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>If I See Her Again</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-19</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G165" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H165" t="str">
-        <v>Maddox Batson</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L165" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>To B Honest</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-19</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Under The Sun</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G166" t="str">
-        <v>4:43</v>
+        <v>4:30</v>
       </c>
       <c r="H166" t="str">
-        <v>Sun-El Musician</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L166" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>To B Honest</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-19</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>To Whom This May Concern</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G167" t="str">
-        <v>4:30</v>
+        <v>2:41</v>
       </c>
       <c r="H167" t="str">
-        <v>Jill Scott</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L167" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Koneko</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-19</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>the beltway is burning</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:41</v>
+        <v>4:08</v>
       </c>
       <c r="H168" t="str">
-        <v>Ekko Astral</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L168" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Koneko</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-19</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Kurage - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:08</v>
+        <v>2:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Liana Flores</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L169" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cupid's Call</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-19</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H170" t="str">
-        <v>Dizzy Fae</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L170" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Pop Off</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-19</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>3:16</v>
       </c>
       <c r="H171" t="str">
-        <v>Chloé Caillet</v>
+        <v>GRiZ</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L171" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Pop Off</v>
+        <v>dreams</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-19</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Pop Off - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:16</v>
+        <v>3:31</v>
       </c>
       <c r="H172" t="str">
-        <v>GRiZ</v>
+        <v>Azzecca</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L172" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>dreams</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-19</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>dreams - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:31</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>Azzecca</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L173" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Love Hate Love</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-19</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H174" t="str">
-        <v>Owen Riegling</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L174" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Do It All Alone</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-19</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G175" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H175" t="str">
-        <v>Rend Collective</v>
+        <v>Cardinals</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L175" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>She Makes Me Real</v>
+        <v>Steady</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-19</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Masquerade</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H176" t="str">
-        <v>Cardinals</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L176" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Steady</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-19</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G177" t="str">
-        <v>3:26</v>
+        <v>2:20</v>
       </c>
       <c r="H177" t="str">
-        <v>Bella Kay</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L177" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>DIRTY TECH</v>
+        <v>Nada Más</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-19</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>PLAY ME</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:20</v>
+        <v>2:19</v>
       </c>
       <c r="H178" t="str">
-        <v>Kim Gordon</v>
+        <v>Tombochio</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L178" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Nada Más</v>
+        <v>Friends Again</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-19</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Nada Más - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H179" t="str">
-        <v>Tombochio</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L179" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Friends Again</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-19</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Friends Again - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:38</v>
+        <v>3:22</v>
       </c>
       <c r="H180" t="str">
-        <v>Baby Rose</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L180" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>W.T.A.</v>
+        <v>desire.</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-19</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>W.T.A. - Single</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G181" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H181" t="str">
-        <v>Isaia Huron</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L181" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>desire.</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-19</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>November Scorpio</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G182" t="str">
-        <v>3:15</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>Tiana Major9</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L182" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-19</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:12</v>
+        <v>4:00</v>
       </c>
       <c r="H183" t="str">
-        <v>August Ponthier</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L183" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Killer Whale</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-19</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Killer Whale - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G184" t="str">
-        <v>4:00</v>
+        <v>2:46</v>
       </c>
       <c r="H184" t="str">
-        <v>Hayden Everett</v>
+        <v>Anjimile</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L184" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Waits for Me</v>
+        <v>Man's World</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-19</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>You’re Free to Go</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G185" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H185" t="str">
-        <v>Anjimile</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L185" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Man's World</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-19</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Mud Blood Bone</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:42</v>
+        <v>3:13</v>
       </c>
       <c r="H186" t="str">
-        <v>Cat Clyde</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L186" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>In the Middle of It</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-19</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:13</v>
+        <v>2:51</v>
       </c>
       <c r="H187" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L187" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-19</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Fleeting - EP</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:51</v>
+        <v>5:23</v>
       </c>
       <c r="H188" t="str">
-        <v>Sarah Kinsley</v>
+        <v>BUNT.</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L188" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-19</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>5:23</v>
+        <v>3:07</v>
       </c>
       <c r="H189" t="str">
-        <v>BUNT.</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L189" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>I've Never Met Her</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-19</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>The Elephant</v>
       </c>
       <c r="G190" t="str">
-        <v>3:07</v>
+        <v>3:28</v>
       </c>
       <c r="H190" t="str">
-        <v>Ally Salort</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L190" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>Yes</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-19</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>The Elephant</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G191" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Ledbyher</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L191" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Yes</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-19</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Just A Few Folk</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:21</v>
+        <v>2:52</v>
       </c>
       <c r="H192" t="str">
-        <v>JP Cooper</v>
+        <v>WesGhost</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L192" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-19</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G193" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H193" t="str">
-        <v>WesGhost</v>
+        <v>Converge</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L193" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Bad Faith</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-19</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Love Is Not Enough</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G194" t="str">
-        <v>2:48</v>
+        <v>4:00</v>
       </c>
       <c r="H194" t="str">
-        <v>Converge</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L194" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-19</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Good God / Baad Man</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:00</v>
+        <v>2:14</v>
       </c>
       <c r="H195" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L195" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Angel Eyes</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-19</v>
@@ -7823,68 +7823,30 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>God Forgives - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G196" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H196" t="str">
-        <v>Guilt Trip</v>
+        <v>Melvins</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L196" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G197" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L197" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -933,7 +933,7 @@
         <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:01</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -2602,7 +2602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Visualizer) - Billy Raffoul and Emily James</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="60">
@@ -3365,7 +3365,7 @@
         <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>2:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -667,7 +667,7 @@
         <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B8" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:59</v>
@@ -705,7 +705,7 @@
         <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:10</v>
@@ -1237,7 +1237,7 @@
         <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:59</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -629,7 +629,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:24</v>
@@ -1199,7 +1199,7 @@
         <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:59</v>
@@ -1769,7 +1769,7 @@
         <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:55</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -4049,7 +4049,7 @@
         <v>Victor Ray - Comfortable - Live from KOKO</v>
       </c>
       <c r="B97" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>5:59</v>
@@ -4125,7 +4125,7 @@
         <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:39</v>
@@ -4163,7 +4163,7 @@
         <v>Nothing But Thieves - Particles (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>3:58</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -1731,7 +1731,7 @@
         <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>5:01</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -3327,7 +3327,7 @@
         <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B78" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:29</v>
@@ -3783,7 +3783,7 @@
         <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B90" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>4:07</v>
@@ -6326,13 +6326,13 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-19</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G157" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H157" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
       </c>
       <c r="L157" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-19</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L158" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-19</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H159" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L159" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-19</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H160" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L160" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-19</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H161" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L161" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-19</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H162" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L162" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-19</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H163" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L163" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-19</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H164" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L164" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-19</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H165" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L165" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-19</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G166" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H166" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L166" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-19</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G167" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H167" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L167" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-19</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G168" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H168" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L168" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-19</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H169" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L169" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-19</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L170" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-19</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L171" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-19</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H172" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L172" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-19</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H173" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L173" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-19</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H174" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L174" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-19</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H175" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L175" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-19</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G176" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L176" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-19</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H177" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L177" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-19</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G178" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L178" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-19</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H179" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L179" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-19</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H180" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L180" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-19</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H181" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L181" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-19</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H182" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L182" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-19</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G183" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H183" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L183" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-19</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H184" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L184" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-19</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G185" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H185" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L185" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-19</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G186" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H186" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L186" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-19</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H187" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L187" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-19</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H188" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L188" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-19</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H189" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L189" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-19</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H190" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L190" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-19</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H191" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L191" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-19</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G192" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H192" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L192" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-19</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H193" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L193" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-19</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G194" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H194" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L194" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-19</v>
@@ -7785,68 +7785,106 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G195" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H195" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L195" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D196" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
+      <c r="D197" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G196" t="str">
+      <c r="G197" t="str">
         <v>3:17</v>
       </c>
-      <c r="H196" t="str">
+      <c r="H197" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K196" t="str">
+      <c r="K197" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L196" t="str">
+      <c r="L197" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:43</v>
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -515,7 +515,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:13</v>
@@ -553,7 +553,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:48</v>
@@ -591,7 +591,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:55</v>
@@ -857,7 +857,7 @@
         <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:09</v>
@@ -1009,7 +1009,7 @@
         <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>5:31</v>
@@ -1161,7 +1161,7 @@
         <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:41</v>
@@ -1617,7 +1617,7 @@
         <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>5:11</v>
@@ -1655,7 +1655,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>2:55</v>
@@ -1693,7 +1693,7 @@
         <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:54</v>
@@ -1845,7 +1845,7 @@
         <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>2:53</v>
@@ -3745,7 +3745,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:47</v>
@@ -4087,7 +4087,7 @@
         <v>Perrie - Woman In Love (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:46</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Trimski</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-19</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Trimski - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G102" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H102" t="str">
-        <v>NAV</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L102" t="str">
-        <v>Trimski - NAV</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="103">
@@ -4502,13 +4502,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-19</v>
@@ -4517,25 +4517,25 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H109" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L109" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="110">
@@ -4578,13 +4578,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-19</v>
@@ -4593,25 +4593,25 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G111" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H111" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L111" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="112">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Woman In Love</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-19</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:43</v>
+        <v>3:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Perrie</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L113" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-19</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H114" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L114" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-19</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G115" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H115" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L115" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-19</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H116" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L116" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-19</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H117" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L117" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-19</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H118" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L118" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-19</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H119" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L119" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-19</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G120" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L120" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-19</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G121" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H121" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L121" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-19</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G122" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H122" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L122" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-19</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H123" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L123" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-19</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H124" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L124" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-19</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G125" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H125" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L125" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-19</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H126" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L126" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-19</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G127" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H127" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L127" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-19</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G128" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L128" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-19</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H129" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L129" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-19</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G130" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H130" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L130" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-19</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H131" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L131" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-19</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H132" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L132" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-19</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H133" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L133" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-19</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G134" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H134" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L134" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-19</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G135" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H135" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L135" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-19</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H136" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L136" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-19</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H137" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L137" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-19</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H138" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L138" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-19</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H139" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L139" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-19</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H140" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L140" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-19</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H141" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L141" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-19</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G142" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H142" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L142" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-19</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H143" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L143" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-19</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L144" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-19</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H145" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L145" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-19</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H146" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L146" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-19</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G147" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H147" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L147" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-19</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H148" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L148" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-19</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H149" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L149" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-19</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G150" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H150" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L150" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-19</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L151" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-19</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L152" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-19</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G153" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H153" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L153" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-19</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G154" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H154" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L154" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-19</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H155" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L155" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-19</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G156" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L156" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-19</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G157" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H157" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L157" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-19</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G158" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
       </c>
       <c r="L158" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-19</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H159" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L159" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-19</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H160" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L160" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-19</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L161" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-19</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G162" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H162" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L162" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-19</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H163" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L163" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-19</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H164" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L164" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-19</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H165" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L165" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-19</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H166" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L166" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-19</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G167" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H167" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L167" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-19</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G168" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H168" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L168" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-19</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G169" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H169" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L169" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-19</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H170" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L170" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-19</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L171" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-19</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H172" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L172" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-19</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L173" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-19</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H174" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L174" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-19</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H175" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L175" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-19</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H176" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L176" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-19</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G177" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H177" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L177" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-19</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H178" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L178" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-19</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G179" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H179" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L179" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-19</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H180" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L180" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-19</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L181" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-19</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H182" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L182" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-19</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G183" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H183" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L183" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-19</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G184" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H184" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L184" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-19</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H185" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L185" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-19</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G186" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H186" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L186" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-19</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G187" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H187" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L187" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-19</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H188" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L188" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-19</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H189" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L189" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-19</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H190" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L190" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-19</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H191" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L191" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-19</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G192" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H192" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L192" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-19</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G193" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H193" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L193" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-19</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H194" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L194" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-19</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G195" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H195" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L195" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-19</v>
@@ -7823,68 +7823,106 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G196" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H196" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L196" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G197" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D197" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
+      <c r="D198" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G197" t="str">
+      <c r="G198" t="str">
         <v>3:17</v>
       </c>
-      <c r="H197" t="str">
+      <c r="H198" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K197" t="str">
+      <c r="K198" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L197" t="str">
+      <c r="L198" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -819,7 +819,7 @@
         <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:35</v>
@@ -895,7 +895,7 @@
         <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:11</v>
@@ -971,7 +971,7 @@
         <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:28</v>
@@ -1085,7 +1085,7 @@
         <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:03</v>
@@ -1123,7 +1123,7 @@
         <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:59</v>
@@ -1389,7 +1389,7 @@
         <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>2:25</v>
@@ -1427,7 +1427,7 @@
         <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:19</v>
@@ -1465,7 +1465,7 @@
         <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:38</v>
@@ -1503,7 +1503,7 @@
         <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>4:05</v>
@@ -1541,7 +1541,7 @@
         <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:46</v>
@@ -1579,7 +1579,7 @@
         <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:25</v>
@@ -1883,7 +1883,7 @@
         <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:30</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -3289,7 +3289,7 @@
         <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B77" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:34</v>
@@ -3631,7 +3631,7 @@
         <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:27</v>
@@ -3669,7 +3669,7 @@
         <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>2:39</v>
@@ -3707,7 +3707,7 @@
         <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:54</v>
@@ -4011,7 +4011,7 @@
         <v>mgk - miss sunshine (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:26</v>
@@ -4201,7 +4201,7 @@
         <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:04</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -781,7 +781,7 @@
         <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>4:26</v>
@@ -3593,7 +3593,7 @@
         <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:56</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -743,7 +743,7 @@
         <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -1047,7 +1047,7 @@
         <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:49</v>
@@ -1351,7 +1351,7 @@
         <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>5:57</v>
@@ -1807,7 +1807,7 @@
         <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:43</v>
@@ -3517,7 +3517,7 @@
         <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B83" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:18</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:58</v>
@@ -1313,7 +1313,7 @@
         <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:10</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
@@ -2103,7 +2103,7 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="46">
@@ -3251,7 +3251,7 @@
         <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:09</v>
@@ -3555,7 +3555,7 @@
         <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B84" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>2:08</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:43</v>
+        <v>2:51</v>
       </c>
       <c r="H2" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:58</v>
+        <v>3:24</v>
       </c>
       <c r="H3" t="str">
-        <v>Catie Turner</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:13</v>
+        <v>4:11</v>
       </c>
       <c r="H4" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>We Three</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:48</v>
+        <v>3:27</v>
       </c>
       <c r="H5" t="str">
-        <v>U2</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:55</v>
+        <v>3:06</v>
       </c>
       <c r="H6" t="str">
-        <v>Lawrence</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:24</v>
+        <v>3:01</v>
       </c>
       <c r="H7" t="str">
-        <v>BUNT. Music</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:59</v>
+        <v>5:38</v>
       </c>
       <c r="H8" t="str">
-        <v>Bruno Mars</v>
+        <v>georgemichael</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -720,7 +720,7 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:10</v>
+        <v>3:43</v>
       </c>
       <c r="H9" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:11</v>
+        <v>2:58</v>
       </c>
       <c r="H10" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:26</v>
+        <v>4:13</v>
       </c>
       <c r="H11" t="str">
-        <v>Neal Francis</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:35</v>
+        <v>5:48</v>
       </c>
       <c r="H12" t="str">
-        <v>mgk</v>
+        <v>U2</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:09</v>
+        <v>3:55</v>
       </c>
       <c r="H13" t="str">
-        <v>Lola Young</v>
+        <v>Lawrence</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:11</v>
+        <v>5:24</v>
       </c>
       <c r="H14" t="str">
-        <v>Holly Humberstone</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:01</v>
+        <v>4:59</v>
       </c>
       <c r="H15" t="str">
-        <v>The Vaccines</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:28</v>
+        <v>2:10</v>
       </c>
       <c r="H16" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,30 +1001,30 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:31</v>
+        <v>3:11</v>
       </c>
       <c r="H17" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:49</v>
+        <v>4:26</v>
       </c>
       <c r="H18" t="str">
-        <v>Mýa</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:03</v>
+        <v>4:35</v>
       </c>
       <c r="H19" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:59</v>
+        <v>2:09</v>
       </c>
       <c r="H20" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Lola Young</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>4:11</v>
       </c>
       <c r="H21" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:59</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>ENHYPEN</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:59</v>
+        <v>3:28</v>
       </c>
       <c r="H23" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>7:48</v>
+        <v>5:31</v>
       </c>
       <c r="H24" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:10</v>
+        <v>2:49</v>
       </c>
       <c r="H25" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Mýa</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>5:57</v>
+        <v>3:03</v>
       </c>
       <c r="H26" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H27" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:19</v>
+        <v>2:41</v>
       </c>
       <c r="H28" t="str">
-        <v>Michael Bolton</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:38</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>mgk</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:05</v>
+        <v>3:59</v>
       </c>
       <c r="H30" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:46</v>
+        <v>7:48</v>
       </c>
       <c r="H31" t="str">
-        <v>Jacob Collier</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:25</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>Victor Ray</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>5:11</v>
+        <v>5:57</v>
       </c>
       <c r="H33" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:55</v>
+        <v>2:25</v>
       </c>
       <c r="H34" t="str">
-        <v>The Warning</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:54</v>
+        <v>3:19</v>
       </c>
       <c r="H35" t="str">
-        <v>The Offspring</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>5:01</v>
+        <v>3:38</v>
       </c>
       <c r="H36" t="str">
-        <v>Caitlyn Smith</v>
+        <v>mgk</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:55</v>
+        <v>4:05</v>
       </c>
       <c r="H37" t="str">
-        <v>HAUSER</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B38" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:43</v>
+        <v>5:46</v>
       </c>
       <c r="H38" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:53</v>
+        <v>3:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Ultra Records</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,21 +1875,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B40" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1898,10 +1898,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:30</v>
+        <v>5:11</v>
       </c>
       <c r="H40" t="str">
-        <v>Anja Kotar</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,21 +1913,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B41" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1936,10 +1936,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:37</v>
+        <v>2:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Michael Bolton</v>
+        <v>The Warning</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B42" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:10</v>
+        <v>4:54</v>
       </c>
       <c r="H42" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Offspring</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:06</v>
+        <v>5:01</v>
       </c>
       <c r="H43" t="str">
-        <v>Alan Walker</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B44" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:17</v>
+        <v>3:55</v>
       </c>
       <c r="H44" t="str">
-        <v>Bruno Mars</v>
+        <v>HAUSER</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:21</v>
+        <v>3:43</v>
       </c>
       <c r="H45" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>6:58</v>
+        <v>2:53</v>
       </c>
       <c r="H46" t="str">
-        <v>Eric Church</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H47" t="str">
-        <v>Meghan Trainor</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:14</v>
+        <v>3:37</v>
       </c>
       <c r="H48" t="str">
-        <v>Ally Salort</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:51</v>
+        <v>4:10</v>
       </c>
       <c r="H49" t="str">
-        <v>Will Swinton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:10</v>
+        <v>3:06</v>
       </c>
       <c r="H50" t="str">
-        <v>elijah woods</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H51" t="str">
-        <v>Jackson Dean</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:51</v>
+        <v>3:21</v>
       </c>
       <c r="H52" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:26</v>
+        <v>6:58</v>
       </c>
       <c r="H53" t="str">
-        <v>Neil Sedaka</v>
+        <v>Eric Church</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:06</v>
+        <v>3:29</v>
       </c>
       <c r="H54" t="str">
-        <v>Sofia Camara</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:04</v>
+        <v>3:14</v>
       </c>
       <c r="H55" t="str">
-        <v>Russell Dickerson</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:03</v>
+        <v>3:51</v>
       </c>
       <c r="H56" t="str">
-        <v>Celine Dion</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:38</v>
+        <v>3:10</v>
       </c>
       <c r="H57" t="str">
-        <v>Bebe Rexha</v>
+        <v>elijah woods</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B58" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H58" t="str">
-        <v>Caroline Jones</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B59" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H59" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B60" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:32</v>
+        <v>3:26</v>
       </c>
       <c r="H60" t="str">
-        <v>Ingrid Andress</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:51</v>
+        <v>3:06</v>
       </c>
       <c r="H61" t="str">
-        <v>MusicByKnox</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:38</v>
+        <v>3:04</v>
       </c>
       <c r="H62" t="str">
-        <v>Ella Langley</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B63" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:26</v>
+        <v>3:03</v>
       </c>
       <c r="H63" t="str">
-        <v>Nickless</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H64" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:08</v>
+        <v>3:29</v>
       </c>
       <c r="H65" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:53</v>
+        <v>2:32</v>
       </c>
       <c r="H66" t="str">
-        <v>August Ponthier</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:10</v>
+        <v>3:32</v>
       </c>
       <c r="H67" t="str">
-        <v>Charli xcx</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:58</v>
+        <v>2:51</v>
       </c>
       <c r="H68" t="str">
-        <v>Caroline Jones</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:44</v>
+        <v>3:38</v>
       </c>
       <c r="H69" t="str">
-        <v>Leah Kate</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B70" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H70" t="str">
-        <v>Troye Sivan</v>
+        <v>Nickless</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:08</v>
+        <v>3:57</v>
       </c>
       <c r="H71" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:09</v>
+        <v>3:08</v>
       </c>
       <c r="H72" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>elijah woods</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:11</v>
+        <v>3:53</v>
       </c>
       <c r="H73" t="str">
-        <v>The Happy Fits</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:02</v>
+        <v>3:10</v>
       </c>
       <c r="H74" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H75" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:09</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Quinn XCII</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:34</v>
+        <v>3:25</v>
       </c>
       <c r="H77" t="str">
-        <v>We Three</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:29</v>
+        <v>4:08</v>
       </c>
       <c r="H78" t="str">
-        <v>A Thousand Horses</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B79" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:51</v>
+        <v>3:09</v>
       </c>
       <c r="H79" t="str">
-        <v>Andrea von Kampen and Lydia Luce</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:56</v>
+        <v>3:11</v>
       </c>
       <c r="H80" t="str">
-        <v>Constant Smiles</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B81" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:25</v>
+        <v>3:02</v>
       </c>
       <c r="H81" t="str">
-        <v>P!NK</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bazzi - moment (Official Audio)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B82" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:33</v>
+        <v>4:20</v>
       </c>
       <c r="H82" t="str">
-        <v>Bazzi</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bazzi - moment (Official Audio) - Bazzi</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B83" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:18</v>
+        <v>4:09</v>
       </c>
       <c r="H83" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B84" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:08</v>
+        <v>4:34</v>
       </c>
       <c r="H84" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>We Three</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bleachers - you and forever (Official Video)</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video )</v>
       </c>
       <c r="B85" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
+        <v>https://www.youtube.com/watch?v=ZDRcnH8zDK4</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:56</v>
+        <v>3:29</v>
       </c>
       <c r="H85" t="str">
-        <v>bleachers</v>
+        <v>A Thousand Horses</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bleachers - you and forever (Official Video) - bleachers</v>
+        <v>A Thousand Horses - Shadows (Featuring Aaron Gillespie) (Official Music Video ) - A Thousand Horses</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Academic – Figure It Out (Official Video)</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
+        <v>https://www.youtube.com/watch?v=GZEmsimT12I</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:27</v>
+        <v>2:51</v>
       </c>
       <c r="H86" t="str">
-        <v>The Academic</v>
+        <v>Andrea von Kampen and Lydia Luce</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
+        <v>These Days - Andrea von Kampen &amp; Lydia Luce (Official Audio) - Andrea von Kampen and Lydia Luce</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
+        <v>https://www.youtube.com/watch?v=L3BICuuaefo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:39</v>
+        <v>2:56</v>
       </c>
       <c r="H87" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Constant Smiles</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
+        <v>Constant Smiles - Everything Is Personal (Official Video) - Constant Smiles</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023)</v>
       </c>
       <c r="B88" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
+        <v>https://www.youtube.com/watch?v=WQptqy_qiFA</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:54</v>
+        <v>3:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Michael Bolton</v>
+        <v>P!NK</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
+        <v>P!NK &amp; Willow Sage Hart - Cover Me In Sunshine (Live From Hyde Park, 2023) - P!NK</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
+        <v>Bazzi - moment (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
+        <v>https://www.youtube.com/watch?v=tM0UBYHmEUM</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:47</v>
+        <v>2:33</v>
       </c>
       <c r="H89" t="str">
-        <v>Caroline Jones</v>
+        <v>Bazzi</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
+        <v>Bazzi - moment (Official Audio) - Bazzi</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B90" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
+        <v>https://www.youtube.com/watch?v=7bN7KOeKkKU</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:07</v>
+        <v>4:18</v>
       </c>
       <c r="H90" t="str">
-        <v>LisaStansfieldtv</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
+        <v>Watch Sabrina Carpenter Take Flight &amp; Soar As She Performs "Manchild" LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B91" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
+        <v>https://www.youtube.com/watch?v=TKlJqOgJg0I</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>5:00</v>
+        <v>2:08</v>
       </c>
       <c r="H91" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
+        <v>sombr Lights Up The Stage Performing “12 to 12” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions)</v>
+        <v>Bleachers - you and forever (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
+        <v>https://www.youtube.com/watch?v=I6ox7VKVzqU</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:27</v>
+        <v>3:56</v>
       </c>
       <c r="H92" t="str">
-        <v>Little Big Town</v>
+        <v>bleachers</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
+        <v>Bleachers - you and forever (Official Video) - bleachers</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
+        <v>The Academic – Figure It Out (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
+        <v>https://www.youtube.com/watch?v=8injrn0jx1M</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>The Academic</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video) - Brigitte Calls Me Baby</v>
+        <v>The Academic – Figure It Out (Official Video) - The Academic</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=394FZz3oU8E</v>
+        <v>https://www.youtube.com/watch?v=QD-V0Q8LjV8</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>10:57</v>
+        <v>2:39</v>
       </c>
       <c r="H94" t="str">
-        <v>JavaJazzFest</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Shakatak "Night Birds" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Louis Tomlinson - Imposter (Lyric Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=fxmIR0LxP3o</v>
+        <v>https://www.youtube.com/watch?v=3vOP_g2XA3w</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:14</v>
+        <v>3:54</v>
       </c>
       <c r="H95" t="str">
-        <v>Robert Grace</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Robert Grace - Follow ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Michael Bolton | My Funny Valentine (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=UhVTCf1Hl3w</v>
+        <v>https://www.youtube.com/watch?v=gb3bbkFsYSI</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:26</v>
+        <v>3:47</v>
       </c>
       <c r="H96" t="str">
-        <v>mgk</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>mgk - miss sunshine (Official Lyric Video) - mgk</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Studio Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary)</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=r_YhMBsAYo0</v>
+        <v>https://www.youtube.com/watch?v=MymvnFD5bVE</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>5:59</v>
+        <v>4:07</v>
       </c>
       <c r="H97" t="str">
-        <v>Victor Ray</v>
+        <v>LisaStansfieldtv</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Victor Ray - Comfortable - Live from KOKO - Victor Ray</v>
+        <v>Lisa Stansfield - Change (US Version) (Real Life Documentary) - LisaStansfieldtv</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Perrie - Woman In Love (Official Audio)</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Xo8bchcDWGg</v>
+        <v>https://www.youtube.com/watch?v=E9AZaIQA9kU</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:46</v>
+        <v>5:00</v>
       </c>
       <c r="H98" t="str">
-        <v>Perrie</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Perrie - Woman In Love (Official Audio) - Perrie</v>
+        <v>Michael Bolton | How Am I Supposed To Live Without You - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer)</v>
+        <v>Little Big Town - Rich Man (Studio Sessions)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=wJBykWfClhI</v>
+        <v>https://www.youtube.com/watch?v=1N3czg7B878</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H99" t="str">
-        <v>Michael Bolton</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Bolton | Eyes On You (Official Visualizer) - Michael Bolton</v>
+        <v>Little Big Town - Rich Man (Studio Sessions) - Little Big Town</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nothing But Thieves - Particles (Official Audio)</v>
+        <v>Brigitte Calls Me Baby - I Danced With Another Love In My Dream (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=uYmT5ouO0Nw</v>
+        <v>https://www.youtube.com/watch?v=RQFDLA0CzEk</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E100" t="str">
